--- a/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_grouped.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_grouped.xlsx
@@ -1436,7 +1436,7 @@
         <v>0.1</v>
       </c>
       <c r="D72" t="n">
-        <v>23.65315948840321</v>
+        <v>18.97804062883935</v>
       </c>
     </row>
     <row r="73">
@@ -4968,13 +4968,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8979A5F-96F6-4045-8088-40A08963C324}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85551A00-98F1-4CA9-B913-D351805A1100}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FAA0857-48D2-4185-AB8B-C874790B46DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92BA2FB8-6CB8-4A94-9BDF-4572E9BE5007}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47F484EB-5178-4F1F-80A5-49868C498E81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B945B8-1819-491F-B945-AA40470B8FAB}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_grouped.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_grouped.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D304"/>
+  <dimension ref="A1:D305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1391,10 +1391,10 @@
         <v>-1.2</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D69" t="n">
-        <v>7.863753664281436</v>
+        <v>19.07175616788135</v>
       </c>
     </row>
     <row r="70">
@@ -1405,10 +1405,10 @@
         <v>-1.2</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>11.24801113340989</v>
+        <v>7.863753664281436</v>
       </c>
     </row>
     <row r="71">
@@ -1416,13 +1416,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D71" t="n">
-        <v>11.94707303482451</v>
+        <v>11.24801113340989</v>
       </c>
     </row>
     <row r="72">
@@ -1433,10 +1433,10 @@
         <v>-1.1</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>18.97804062883935</v>
+        <v>12.01511145919841</v>
       </c>
     </row>
     <row r="73">
@@ -1447,10 +1447,10 @@
         <v>-1.1</v>
       </c>
       <c r="C73" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D73" t="n">
-        <v>9.340313376676379</v>
+        <v>20.21312670289172</v>
       </c>
     </row>
     <row r="74">
@@ -1461,10 +1461,10 @@
         <v>-1.1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D74" t="n">
-        <v>11.49238646524473</v>
+        <v>9.340313376676379</v>
       </c>
     </row>
     <row r="75">
@@ -1472,13 +1472,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D75" t="n">
-        <v>-10.10953812013922</v>
+        <v>11.49238646524473</v>
       </c>
     </row>
     <row r="76">
@@ -1489,10 +1489,10 @@
         <v>-1</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D76" t="n">
-        <v>-5.92621924840283</v>
+        <v>-10.10953812013922</v>
       </c>
     </row>
     <row r="77">
@@ -1503,10 +1503,10 @@
         <v>-1</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="D77" t="n">
-        <v>11.59621764602354</v>
+        <v>-5.92621924840283</v>
       </c>
     </row>
     <row r="78">
@@ -1517,10 +1517,10 @@
         <v>-1</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D78" t="n">
-        <v>20.15641168256447</v>
+        <v>11.59621764602354</v>
       </c>
     </row>
     <row r="79">
@@ -1531,10 +1531,10 @@
         <v>-1</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D79" t="n">
-        <v>7.562179536973295</v>
+        <v>20.15641168256447</v>
       </c>
     </row>
     <row r="80">
@@ -1542,13 +1542,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="D80" t="n">
-        <v>17.31903482350436</v>
+        <v>7.562179536973295</v>
       </c>
     </row>
     <row r="81">
@@ -1559,10 +1559,10 @@
         <v>-0.9</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D81" t="n">
-        <v>19.5534934785758</v>
+        <v>17.31903482350436</v>
       </c>
     </row>
     <row r="82">
@@ -1573,10 +1573,10 @@
         <v>-0.9</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D82" t="n">
-        <v>9.150304569791889</v>
+        <v>19.5534934785758</v>
       </c>
     </row>
     <row r="83">
@@ -1587,10 +1587,10 @@
         <v>-0.9</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D83" t="n">
-        <v>17.13330513789267</v>
+        <v>9.150304569791889</v>
       </c>
     </row>
     <row r="84">
@@ -1601,10 +1601,10 @@
         <v>-0.9</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>10.01856323137027</v>
+        <v>17.13330513789267</v>
       </c>
     </row>
     <row r="85">
@@ -1615,10 +1615,10 @@
         <v>-0.9</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D85" t="n">
-        <v>25.84651511002527</v>
+        <v>10.01856323137027</v>
       </c>
     </row>
     <row r="86">
@@ -1629,10 +1629,10 @@
         <v>-0.9</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D86" t="n">
-        <v>2.775317121015397</v>
+        <v>25.84651511002527</v>
       </c>
     </row>
     <row r="87">
@@ -1643,10 +1643,10 @@
         <v>-0.9</v>
       </c>
       <c r="C87" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D87" t="n">
-        <v>8.010909403402721</v>
+        <v>2.775317121015397</v>
       </c>
     </row>
     <row r="88">
@@ -1654,13 +1654,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D88" t="n">
-        <v>32.49688209597053</v>
+        <v>8.010909403402721</v>
       </c>
     </row>
     <row r="89">
@@ -1671,10 +1671,10 @@
         <v>-0.8</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D89" t="n">
-        <v>-4.245257729307916</v>
+        <v>32.49688209597053</v>
       </c>
     </row>
     <row r="90">
@@ -1685,10 +1685,10 @@
         <v>-0.8</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D90" t="n">
-        <v>16.59444445072643</v>
+        <v>-4.245257729307916</v>
       </c>
     </row>
     <row r="91">
@@ -1699,10 +1699,10 @@
         <v>-0.8</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D91" t="n">
-        <v>16.36696596059325</v>
+        <v>16.59444445072643</v>
       </c>
     </row>
     <row r="92">
@@ -1713,10 +1713,10 @@
         <v>-0.8</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>7.359221554684029</v>
+        <v>16.36696596059325</v>
       </c>
     </row>
     <row r="93">
@@ -1727,10 +1727,10 @@
         <v>-0.8</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D93" t="n">
-        <v>7.447912052149815</v>
+        <v>7.359221554684029</v>
       </c>
     </row>
     <row r="94">
@@ -1741,10 +1741,10 @@
         <v>-0.8</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D94" t="n">
-        <v>13.5225535827757</v>
+        <v>7.447912052149815</v>
       </c>
     </row>
     <row r="95">
@@ -1755,10 +1755,10 @@
         <v>-0.8</v>
       </c>
       <c r="C95" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D95" t="n">
-        <v>3.760721630210839</v>
+        <v>13.5225535827757</v>
       </c>
     </row>
     <row r="96">
@@ -1766,13 +1766,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D96" t="n">
-        <v>-3.295103945896905</v>
+        <v>3.760721630210839</v>
       </c>
     </row>
     <row r="97">
@@ -1783,10 +1783,10 @@
         <v>-0.7</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D97" t="n">
-        <v>8.854013381408961</v>
+        <v>-3.295103945896905</v>
       </c>
     </row>
     <row r="98">
@@ -1797,10 +1797,10 @@
         <v>-0.7</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D98" t="n">
-        <v>10.10934734452611</v>
+        <v>8.854013381408961</v>
       </c>
     </row>
     <row r="99">
@@ -1811,10 +1811,10 @@
         <v>-0.7</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>12.45005147499743</v>
+        <v>10.10934734452611</v>
       </c>
     </row>
     <row r="100">
@@ -1825,10 +1825,10 @@
         <v>-0.7</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D100" t="n">
-        <v>28.25584185685916</v>
+        <v>12.45005147499743</v>
       </c>
     </row>
     <row r="101">
@@ -1836,13 +1836,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D101" t="n">
-        <v>38.40703381314563</v>
+        <v>28.25584185685916</v>
       </c>
     </row>
     <row r="102">
@@ -1853,10 +1853,10 @@
         <v>-0.6</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="D102" t="n">
-        <v>9.610479570395958</v>
+        <v>38.40703381314563</v>
       </c>
     </row>
     <row r="103">
@@ -1867,10 +1867,10 @@
         <v>-0.6</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D103" t="n">
-        <v>6.257388578121698</v>
+        <v>9.610479570395958</v>
       </c>
     </row>
     <row r="104">
@@ -1881,10 +1881,10 @@
         <v>-0.6</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D104" t="n">
-        <v>9.914194347595121</v>
+        <v>6.257388578121698</v>
       </c>
     </row>
     <row r="105">
@@ -1895,10 +1895,10 @@
         <v>-0.6</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D105" t="n">
-        <v>15.82025254968401</v>
+        <v>9.914194347595121</v>
       </c>
     </row>
     <row r="106">
@@ -1909,10 +1909,10 @@
         <v>-0.6</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>16.57553971333769</v>
+        <v>15.82025254968401</v>
       </c>
     </row>
     <row r="107">
@@ -1923,10 +1923,10 @@
         <v>-0.6</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D107" t="n">
-        <v>6.012699659193837</v>
+        <v>16.57553971333769</v>
       </c>
     </row>
     <row r="108">
@@ -1937,10 +1937,10 @@
         <v>-0.6</v>
       </c>
       <c r="C108" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D108" t="n">
-        <v>22.56158446324479</v>
+        <v>6.012699659193837</v>
       </c>
     </row>
     <row r="109">
@@ -1951,10 +1951,10 @@
         <v>-0.6</v>
       </c>
       <c r="C109" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D109" t="n">
-        <v>27.63714927361014</v>
+        <v>22.56158446324479</v>
       </c>
     </row>
     <row r="110">
@@ -1962,13 +1962,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D110" t="n">
-        <v>8.898772015691709</v>
+        <v>27.63714927361014</v>
       </c>
     </row>
     <row r="111">
@@ -1979,10 +1979,10 @@
         <v>-0.5</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D111" t="n">
-        <v>5.406472437959754</v>
+        <v>8.898772015691709</v>
       </c>
     </row>
     <row r="112">
@@ -1993,10 +1993,10 @@
         <v>-0.5</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D112" t="n">
-        <v>20.89983643824696</v>
+        <v>5.406472437959754</v>
       </c>
     </row>
     <row r="113">
@@ -2007,10 +2007,10 @@
         <v>-0.5</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D113" t="n">
-        <v>22.71840750732937</v>
+        <v>20.89983643824696</v>
       </c>
     </row>
     <row r="114">
@@ -2021,10 +2021,10 @@
         <v>-0.5</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>20.73020246429007</v>
+        <v>22.71840750732937</v>
       </c>
     </row>
     <row r="115">
@@ -2035,10 +2035,10 @@
         <v>-0.5</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D115" t="n">
-        <v>14.12591159576888</v>
+        <v>20.73020246429007</v>
       </c>
     </row>
     <row r="116">
@@ -2049,10 +2049,10 @@
         <v>-0.5</v>
       </c>
       <c r="C116" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D116" t="n">
-        <v>13.35039006591945</v>
+        <v>14.12591159576888</v>
       </c>
     </row>
     <row r="117">
@@ -2063,10 +2063,10 @@
         <v>-0.5</v>
       </c>
       <c r="C117" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D117" t="n">
-        <v>21.84679967196988</v>
+        <v>13.35039006591945</v>
       </c>
     </row>
     <row r="118">
@@ -2074,13 +2074,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D118" t="n">
-        <v>-3.586847936385662</v>
+        <v>21.84679967196988</v>
       </c>
     </row>
     <row r="119">
@@ -2091,10 +2091,10 @@
         <v>-0.4</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D119" t="n">
-        <v>22.30386193208223</v>
+        <v>-3.586847936385662</v>
       </c>
     </row>
     <row r="120">
@@ -2105,10 +2105,10 @@
         <v>-0.4</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D120" t="n">
-        <v>15.05120190401821</v>
+        <v>22.30386193208223</v>
       </c>
     </row>
     <row r="121">
@@ -2119,10 +2119,10 @@
         <v>-0.4</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>15.44754024392076</v>
+        <v>15.05120190401821</v>
       </c>
     </row>
     <row r="122">
@@ -2133,10 +2133,10 @@
         <v>-0.4</v>
       </c>
       <c r="C122" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D122" t="n">
-        <v>22.10829809189676</v>
+        <v>15.44754024392076</v>
       </c>
     </row>
     <row r="123">
@@ -2147,10 +2147,10 @@
         <v>-0.4</v>
       </c>
       <c r="C123" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D123" t="n">
-        <v>19.72421963246074</v>
+        <v>22.10829809189676</v>
       </c>
     </row>
     <row r="124">
@@ -2161,10 +2161,10 @@
         <v>-0.4</v>
       </c>
       <c r="C124" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D124" t="n">
-        <v>16.50016608436669</v>
+        <v>19.72421963246074</v>
       </c>
     </row>
     <row r="125">
@@ -2172,13 +2172,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D125" t="n">
-        <v>35.31524330966344</v>
+        <v>16.50016608436669</v>
       </c>
     </row>
     <row r="126">
@@ -2189,10 +2189,10 @@
         <v>-0.3</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D126" t="n">
-        <v>4.343892684273276</v>
+        <v>35.31524330966344</v>
       </c>
     </row>
     <row r="127">
@@ -2203,10 +2203,10 @@
         <v>-0.3</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D127" t="n">
-        <v>-3.18058767263614</v>
+        <v>4.343892684273276</v>
       </c>
     </row>
     <row r="128">
@@ -2217,10 +2217,10 @@
         <v>-0.3</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D128" t="n">
-        <v>20.54730769394918</v>
+        <v>-3.18058767263614</v>
       </c>
     </row>
     <row r="129">
@@ -2231,10 +2231,10 @@
         <v>-0.3</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>8.707759284382448</v>
+        <v>20.54730769394918</v>
       </c>
     </row>
     <row r="130">
@@ -2245,10 +2245,10 @@
         <v>-0.3</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D130" t="n">
-        <v>25.2898350113473</v>
+        <v>8.707759284382448</v>
       </c>
     </row>
     <row r="131">
@@ -2259,10 +2259,10 @@
         <v>-0.3</v>
       </c>
       <c r="C131" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D131" t="n">
-        <v>11.26840126060807</v>
+        <v>25.2898350113473</v>
       </c>
     </row>
     <row r="132">
@@ -2270,13 +2270,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D132" t="n">
-        <v>13.52806940157711</v>
+        <v>11.26840126060807</v>
       </c>
     </row>
     <row r="133">
@@ -2287,10 +2287,10 @@
         <v>-0.2</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="D133" t="n">
-        <v>24.74071716269537</v>
+        <v>13.52806940157711</v>
       </c>
     </row>
     <row r="134">
@@ -2301,10 +2301,10 @@
         <v>-0.2</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D134" t="n">
-        <v>13.99908566516049</v>
+        <v>24.74071716269537</v>
       </c>
     </row>
     <row r="135">
@@ -2315,10 +2315,10 @@
         <v>-0.2</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>13.0840098349689</v>
+        <v>13.99908566516049</v>
       </c>
     </row>
     <row r="136">
@@ -2329,10 +2329,10 @@
         <v>-0.2</v>
       </c>
       <c r="C136" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D136" t="n">
-        <v>29.40056985998893</v>
+        <v>13.0840098349689</v>
       </c>
     </row>
     <row r="137">
@@ -2343,10 +2343,10 @@
         <v>-0.2</v>
       </c>
       <c r="C137" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D137" t="n">
-        <v>11.99860786056441</v>
+        <v>29.40056985998893</v>
       </c>
     </row>
     <row r="138">
@@ -2357,10 +2357,10 @@
         <v>-0.2</v>
       </c>
       <c r="C138" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="D138" t="n">
-        <v>11.62716768865067</v>
+        <v>11.99860786056441</v>
       </c>
     </row>
     <row r="139">
@@ -2368,13 +2368,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D139" t="n">
-        <v>38.03317170768623</v>
+        <v>11.62716768865067</v>
       </c>
     </row>
     <row r="140">
@@ -2385,10 +2385,10 @@
         <v>-0.1</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="D140" t="n">
-        <v>26.13664646256055</v>
+        <v>38.03317170768623</v>
       </c>
     </row>
     <row r="141">
@@ -2399,10 +2399,10 @@
         <v>-0.1</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="D141" t="n">
-        <v>21.49294428478238</v>
+        <v>26.13664646256055</v>
       </c>
     </row>
     <row r="142">
@@ -2413,10 +2413,10 @@
         <v>-0.1</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D142" t="n">
-        <v>10.39918451703468</v>
+        <v>21.49294428478238</v>
       </c>
     </row>
     <row r="143">
@@ -2427,10 +2427,10 @@
         <v>-0.1</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>9.107548918683161</v>
+        <v>10.39918451703468</v>
       </c>
     </row>
     <row r="144">
@@ -2441,10 +2441,10 @@
         <v>-0.1</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D144" t="n">
-        <v>11.86945294864077</v>
+        <v>9.107548918683161</v>
       </c>
     </row>
     <row r="145">
@@ -2455,10 +2455,10 @@
         <v>-0.1</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D145" t="n">
-        <v>29.40242982712884</v>
+        <v>11.86945294864077</v>
       </c>
     </row>
     <row r="146">
@@ -2469,10 +2469,10 @@
         <v>-0.1</v>
       </c>
       <c r="C146" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D146" t="n">
-        <v>-6.304089349534692</v>
+        <v>29.40242982712884</v>
       </c>
     </row>
     <row r="147">
@@ -2480,13 +2480,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D147" t="n">
-        <v>12.887136334722</v>
+        <v>-6.304089349534692</v>
       </c>
     </row>
     <row r="148">
@@ -2497,10 +2497,10 @@
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D148" t="n">
-        <v>15.24618485365237</v>
+        <v>12.887136334722</v>
       </c>
     </row>
     <row r="149">
@@ -2511,10 +2511,10 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>15.2203514657723</v>
+        <v>15.24618485365237</v>
       </c>
     </row>
     <row r="150">
@@ -2525,10 +2525,10 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D150" t="n">
-        <v>16.6414844089368</v>
+        <v>15.2203514657723</v>
       </c>
     </row>
     <row r="151">
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D151" t="n">
-        <v>12.34534228433971</v>
+        <v>16.6414844089368</v>
       </c>
     </row>
     <row r="152">
@@ -2550,13 +2550,13 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>-1.8</v>
+        <v>0.3</v>
       </c>
       <c r="D152" t="n">
-        <v>20.65558253568762</v>
+        <v>12.34534228433971</v>
       </c>
     </row>
     <row r="153">
@@ -2567,10 +2567,10 @@
         <v>0.1</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="D153" t="n">
-        <v>21.93524042214195</v>
+        <v>20.65558253568762</v>
       </c>
     </row>
     <row r="154">
@@ -2581,10 +2581,10 @@
         <v>0.1</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>12.95881016986827</v>
+        <v>21.93524042214195</v>
       </c>
     </row>
     <row r="155">
@@ -2595,10 +2595,10 @@
         <v>0.1</v>
       </c>
       <c r="C155" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D155" t="n">
-        <v>20.51006817005711</v>
+        <v>12.95881016986827</v>
       </c>
     </row>
     <row r="156">
@@ -2606,13 +2606,13 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C156" t="n">
         <v>0.2</v>
       </c>
-      <c r="C156" t="n">
-        <v>-0.8</v>
-      </c>
       <c r="D156" t="n">
-        <v>8.675499305158517</v>
+        <v>20.51006817005711</v>
       </c>
     </row>
     <row r="157">
@@ -2623,10 +2623,10 @@
         <v>0.2</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="D157" t="n">
-        <v>11.73274125115487</v>
+        <v>8.675499305158517</v>
       </c>
     </row>
     <row r="158">
@@ -2637,10 +2637,10 @@
         <v>0.2</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D158" t="n">
-        <v>-10.48272761205174</v>
+        <v>11.73274125115487</v>
       </c>
     </row>
     <row r="159">
@@ -2651,10 +2651,10 @@
         <v>0.2</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D159" t="n">
-        <v>-4.102810132891062</v>
+        <v>-10.48272761205174</v>
       </c>
     </row>
     <row r="160">
@@ -2665,10 +2665,10 @@
         <v>0.2</v>
       </c>
       <c r="C160" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="D160" t="n">
-        <v>22.24487931933098</v>
+        <v>-4.102810132891062</v>
       </c>
     </row>
     <row r="161">
@@ -2679,10 +2679,10 @@
         <v>0.2</v>
       </c>
       <c r="C161" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D161" t="n">
-        <v>9.03314495772889</v>
+        <v>22.24487931933098</v>
       </c>
     </row>
     <row r="162">
@@ -2693,10 +2693,10 @@
         <v>0.2</v>
       </c>
       <c r="C162" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D162" t="n">
-        <v>12.89231662866284</v>
+        <v>9.03314495772889</v>
       </c>
     </row>
     <row r="163">
@@ -2704,13 +2704,13 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C163" t="n">
         <v>0.3</v>
       </c>
-      <c r="C163" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="D163" t="n">
-        <v>34.3200087534147</v>
+        <v>12.89231662866284</v>
       </c>
     </row>
     <row r="164">
@@ -2721,10 +2721,10 @@
         <v>0.3</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="D164" t="n">
-        <v>-7.220868045776685</v>
+        <v>34.3200087534147</v>
       </c>
     </row>
     <row r="165">
@@ -2735,10 +2735,10 @@
         <v>0.3</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D165" t="n">
-        <v>22.68607581675329</v>
+        <v>-7.220868045776685</v>
       </c>
     </row>
     <row r="166">
@@ -2749,10 +2749,10 @@
         <v>0.3</v>
       </c>
       <c r="C166" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>17.25238272973596</v>
+        <v>22.68607581675329</v>
       </c>
     </row>
     <row r="167">
@@ -2763,10 +2763,10 @@
         <v>0.3</v>
       </c>
       <c r="C167" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D167" t="n">
-        <v>13.65983021502197</v>
+        <v>17.25238272973596</v>
       </c>
     </row>
     <row r="168">
@@ -2774,13 +2774,13 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C168" t="n">
         <v>0.4</v>
       </c>
-      <c r="C168" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="D168" t="n">
-        <v>16.24970313980212</v>
+        <v>13.65983021502197</v>
       </c>
     </row>
     <row r="169">
@@ -2791,10 +2791,10 @@
         <v>0.4</v>
       </c>
       <c r="C169" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="D169" t="n">
-        <v>8.724666083835872</v>
+        <v>16.24970313980212</v>
       </c>
     </row>
     <row r="170">
@@ -2805,10 +2805,10 @@
         <v>0.4</v>
       </c>
       <c r="C170" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D170" t="n">
-        <v>14.59002027965239</v>
+        <v>8.724666083835872</v>
       </c>
     </row>
     <row r="171">
@@ -2819,10 +2819,10 @@
         <v>0.4</v>
       </c>
       <c r="C171" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D171" t="n">
-        <v>7.080409836316237</v>
+        <v>14.59002027965239</v>
       </c>
     </row>
     <row r="172">
@@ -2830,13 +2830,13 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D172" t="n">
-        <v>-35.69907125330158</v>
+        <v>7.080409836316237</v>
       </c>
     </row>
     <row r="173">
@@ -2847,10 +2847,10 @@
         <v>0.5</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D173" t="n">
-        <v>-2.528977258676479</v>
+        <v>-35.69907125330158</v>
       </c>
     </row>
     <row r="174">
@@ -2861,10 +2861,10 @@
         <v>0.5</v>
       </c>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D174" t="n">
-        <v>8.959448245783976</v>
+        <v>-2.528977258676479</v>
       </c>
     </row>
     <row r="175">
@@ -2875,10 +2875,10 @@
         <v>0.5</v>
       </c>
       <c r="C175" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>4.562753904953365</v>
+        <v>8.959448245783976</v>
       </c>
     </row>
     <row r="176">
@@ -2889,10 +2889,10 @@
         <v>0.5</v>
       </c>
       <c r="C176" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D176" t="n">
-        <v>16.85459832183653</v>
+        <v>4.562753904953365</v>
       </c>
     </row>
     <row r="177">
@@ -2903,10 +2903,10 @@
         <v>0.5</v>
       </c>
       <c r="C177" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D177" t="n">
-        <v>11.30381646904931</v>
+        <v>16.85459832183653</v>
       </c>
     </row>
     <row r="178">
@@ -2917,10 +2917,10 @@
         <v>0.5</v>
       </c>
       <c r="C178" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D178" t="n">
-        <v>-6.332076215563898</v>
+        <v>11.30381646904931</v>
       </c>
     </row>
     <row r="179">
@@ -2928,13 +2928,13 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D179" t="n">
-        <v>23.31763820152588</v>
+        <v>-6.332076215563898</v>
       </c>
     </row>
     <row r="180">
@@ -2945,10 +2945,10 @@
         <v>0.6</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D180" t="n">
-        <v>9.003359893565621</v>
+        <v>23.31763820152588</v>
       </c>
     </row>
     <row r="181">
@@ -2959,10 +2959,10 @@
         <v>0.6</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="D181" t="n">
-        <v>17.68825690676043</v>
+        <v>9.003359893565621</v>
       </c>
     </row>
     <row r="182">
@@ -2973,10 +2973,10 @@
         <v>0.6</v>
       </c>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D182" t="n">
-        <v>6.236663804781623</v>
+        <v>17.68825690676043</v>
       </c>
     </row>
     <row r="183">
@@ -2987,10 +2987,10 @@
         <v>0.6</v>
       </c>
       <c r="C183" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>26.46960405199754</v>
+        <v>6.236663804781623</v>
       </c>
     </row>
     <row r="184">
@@ -3001,10 +3001,10 @@
         <v>0.6</v>
       </c>
       <c r="C184" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D184" t="n">
-        <v>20.20773014373248</v>
+        <v>26.46960405199754</v>
       </c>
     </row>
     <row r="185">
@@ -3015,10 +3015,10 @@
         <v>0.6</v>
       </c>
       <c r="C185" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D185" t="n">
-        <v>15.44676767833113</v>
+        <v>20.20773014373248</v>
       </c>
     </row>
     <row r="186">
@@ -3026,13 +3026,13 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D186" t="n">
-        <v>17.86620487654922</v>
+        <v>15.44676767833113</v>
       </c>
     </row>
     <row r="187">
@@ -3043,10 +3043,10 @@
         <v>0.7</v>
       </c>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D187" t="n">
-        <v>-3.145568089499773</v>
+        <v>17.86620487654922</v>
       </c>
     </row>
     <row r="188">
@@ -3057,10 +3057,10 @@
         <v>0.7</v>
       </c>
       <c r="C188" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>24.39952726530608</v>
+        <v>-3.145568089499773</v>
       </c>
     </row>
     <row r="189">
@@ -3071,10 +3071,10 @@
         <v>0.7</v>
       </c>
       <c r="C189" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D189" t="n">
-        <v>22.14445093028229</v>
+        <v>24.39952726530608</v>
       </c>
     </row>
     <row r="190">
@@ -3085,10 +3085,10 @@
         <v>0.7</v>
       </c>
       <c r="C190" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D190" t="n">
-        <v>-8.539851952354704</v>
+        <v>22.14445093028229</v>
       </c>
     </row>
     <row r="191">
@@ -3096,13 +3096,13 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D191" t="n">
-        <v>-36.32794889204803</v>
+        <v>-8.539851952354704</v>
       </c>
     </row>
     <row r="192">
@@ -3113,10 +3113,10 @@
         <v>0.8</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D192" t="n">
-        <v>-40.90711089487865</v>
+        <v>-36.32794889204803</v>
       </c>
     </row>
     <row r="193">
@@ -3127,10 +3127,10 @@
         <v>0.8</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="D193" t="n">
-        <v>-13.37967884285289</v>
+        <v>-40.90711089487865</v>
       </c>
     </row>
     <row r="194">
@@ -3141,10 +3141,10 @@
         <v>0.8</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D194" t="n">
-        <v>2.42507817976994</v>
+        <v>-13.37967884285289</v>
       </c>
     </row>
     <row r="195">
@@ -3155,10 +3155,10 @@
         <v>0.8</v>
       </c>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D195" t="n">
-        <v>16.79126653912467</v>
+        <v>2.42507817976994</v>
       </c>
     </row>
     <row r="196">
@@ -3169,10 +3169,10 @@
         <v>0.8</v>
       </c>
       <c r="C196" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>18.84562481075803</v>
+        <v>16.79126653912467</v>
       </c>
     </row>
     <row r="197">
@@ -3183,10 +3183,10 @@
         <v>0.8</v>
       </c>
       <c r="C197" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D197" t="n">
-        <v>1.630749191837651</v>
+        <v>18.84562481075803</v>
       </c>
     </row>
     <row r="198">
@@ -3194,13 +3194,13 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D198" t="n">
-        <v>16.96832641513663</v>
+        <v>1.630749191837651</v>
       </c>
     </row>
     <row r="199">
@@ -3211,10 +3211,10 @@
         <v>0.9</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="D199" t="n">
-        <v>9.667322606019651</v>
+        <v>16.96832641513663</v>
       </c>
     </row>
     <row r="200">
@@ -3225,10 +3225,10 @@
         <v>0.9</v>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D200" t="n">
-        <v>16.93508581405908</v>
+        <v>9.667322606019651</v>
       </c>
     </row>
     <row r="201">
@@ -3239,10 +3239,10 @@
         <v>0.9</v>
       </c>
       <c r="C201" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>11.25068766258671</v>
+        <v>16.93508581405908</v>
       </c>
     </row>
     <row r="202">
@@ -3253,10 +3253,10 @@
         <v>0.9</v>
       </c>
       <c r="C202" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D202" t="n">
-        <v>21.68034025664982</v>
+        <v>11.25068766258671</v>
       </c>
     </row>
     <row r="203">
@@ -3267,10 +3267,10 @@
         <v>0.9</v>
       </c>
       <c r="C203" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D203" t="n">
-        <v>10.01949013751486</v>
+        <v>21.68034025664982</v>
       </c>
     </row>
     <row r="204">
@@ -3278,13 +3278,13 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.9</v>
+        <v>0.3</v>
       </c>
       <c r="D204" t="n">
-        <v>9.338123687716626</v>
+        <v>10.01949013751486</v>
       </c>
     </row>
     <row r="205">
@@ -3295,10 +3295,10 @@
         <v>1</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="D205" t="n">
-        <v>-38.98932234183646</v>
+        <v>9.338123687716626</v>
       </c>
     </row>
     <row r="206">
@@ -3309,10 +3309,10 @@
         <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D206" t="n">
-        <v>-4.049027247638014</v>
+        <v>-38.98932234183646</v>
       </c>
     </row>
     <row r="207">
@@ -3323,10 +3323,10 @@
         <v>1</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D207" t="n">
-        <v>11.28699341118687</v>
+        <v>-4.049027247638014</v>
       </c>
     </row>
     <row r="208">
@@ -3337,10 +3337,10 @@
         <v>1</v>
       </c>
       <c r="C208" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D208" t="n">
-        <v>16.41663227719419</v>
+        <v>11.28699341118687</v>
       </c>
     </row>
     <row r="209">
@@ -3351,10 +3351,10 @@
         <v>1</v>
       </c>
       <c r="C209" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>26.94742380345686</v>
+        <v>16.41663227719419</v>
       </c>
     </row>
     <row r="210">
@@ -3365,10 +3365,10 @@
         <v>1</v>
       </c>
       <c r="C210" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D210" t="n">
-        <v>6.875770128986824</v>
+        <v>26.94742380345686</v>
       </c>
     </row>
     <row r="211">
@@ -3379,10 +3379,10 @@
         <v>1</v>
       </c>
       <c r="C211" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D211" t="n">
-        <v>-1.835302430313079</v>
+        <v>6.875770128986824</v>
       </c>
     </row>
     <row r="212">
@@ -3390,13 +3390,13 @@
         <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.9</v>
+        <v>0.3</v>
       </c>
       <c r="D212" t="n">
-        <v>-11.52350378740865</v>
+        <v>-1.835302430313079</v>
       </c>
     </row>
     <row r="213">
@@ -3407,10 +3407,10 @@
         <v>1.1</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="D213" t="n">
-        <v>-33.78434889108475</v>
+        <v>-11.52350378740865</v>
       </c>
     </row>
     <row r="214">
@@ -3421,10 +3421,10 @@
         <v>1.1</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="D214" t="n">
-        <v>-17.19746097743489</v>
+        <v>-33.78434889108475</v>
       </c>
     </row>
     <row r="215">
@@ -3435,10 +3435,10 @@
         <v>1.1</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D215" t="n">
-        <v>-6.329827177057583</v>
+        <v>-17.19746097743489</v>
       </c>
     </row>
     <row r="216">
@@ -3449,10 +3449,10 @@
         <v>1.1</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D216" t="n">
-        <v>-14.54650273182927</v>
+        <v>-6.329827177057583</v>
       </c>
     </row>
     <row r="217">
@@ -3463,10 +3463,10 @@
         <v>1.1</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D217" t="n">
-        <v>16.30970776998776</v>
+        <v>-14.54650273182927</v>
       </c>
     </row>
     <row r="218">
@@ -3477,10 +3477,10 @@
         <v>1.1</v>
       </c>
       <c r="C218" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D218" t="n">
-        <v>24.00882805268154</v>
+        <v>16.30970776998776</v>
       </c>
     </row>
     <row r="219">
@@ -3491,10 +3491,10 @@
         <v>1.1</v>
       </c>
       <c r="C219" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>11.34361638072524</v>
+        <v>24.00882805268154</v>
       </c>
     </row>
     <row r="220">
@@ -3505,10 +3505,10 @@
         <v>1.1</v>
       </c>
       <c r="C220" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D220" t="n">
-        <v>20.34583240600429</v>
+        <v>11.34361638072524</v>
       </c>
     </row>
     <row r="221">
@@ -3519,10 +3519,10 @@
         <v>1.1</v>
       </c>
       <c r="C221" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D221" t="n">
-        <v>6.944038309892764</v>
+        <v>20.34583240600429</v>
       </c>
     </row>
     <row r="222">
@@ -3530,13 +3530,13 @@
         <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D222" t="n">
-        <v>19.3669824082265</v>
+        <v>6.944038309892764</v>
       </c>
     </row>
     <row r="223">
@@ -3547,10 +3547,10 @@
         <v>1.2</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D223" t="n">
-        <v>16.03281290805518</v>
+        <v>19.3669824082265</v>
       </c>
     </row>
     <row r="224">
@@ -3561,10 +3561,10 @@
         <v>1.2</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="D224" t="n">
-        <v>3.232635306549387</v>
+        <v>16.03281290805518</v>
       </c>
     </row>
     <row r="225">
@@ -3575,10 +3575,10 @@
         <v>1.2</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D225" t="n">
-        <v>13.10476113223896</v>
+        <v>3.232635306549387</v>
       </c>
     </row>
     <row r="226">
@@ -3589,10 +3589,10 @@
         <v>1.2</v>
       </c>
       <c r="C226" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D226" t="n">
-        <v>17.06758547212501</v>
+        <v>13.10476113223896</v>
       </c>
     </row>
     <row r="227">
@@ -3603,10 +3603,10 @@
         <v>1.2</v>
       </c>
       <c r="C227" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0.222349113221143</v>
+        <v>17.06758547212501</v>
       </c>
     </row>
     <row r="228">
@@ -3617,10 +3617,10 @@
         <v>1.2</v>
       </c>
       <c r="C228" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D228" t="n">
-        <v>22.88014297715828</v>
+        <v>0.222349113221143</v>
       </c>
     </row>
     <row r="229">
@@ -3631,10 +3631,10 @@
         <v>1.2</v>
       </c>
       <c r="C229" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D229" t="n">
-        <v>10.9473752070705</v>
+        <v>22.88014297715828</v>
       </c>
     </row>
     <row r="230">
@@ -3645,10 +3645,10 @@
         <v>1.2</v>
       </c>
       <c r="C230" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D230" t="n">
-        <v>12.96867848991812</v>
+        <v>10.9473752070705</v>
       </c>
     </row>
     <row r="231">
@@ -3656,13 +3656,13 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D231" t="n">
-        <v>-16.93000735742697</v>
+        <v>12.96867848991812</v>
       </c>
     </row>
     <row r="232">
@@ -3673,10 +3673,10 @@
         <v>1.3</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="D232" t="n">
-        <v>-1.950876454962897</v>
+        <v>-16.93000735742697</v>
       </c>
     </row>
     <row r="233">
@@ -3687,10 +3687,10 @@
         <v>1.3</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D233" t="n">
-        <v>14.85167800881492</v>
+        <v>-1.950876454962897</v>
       </c>
     </row>
     <row r="234">
@@ -3701,10 +3701,10 @@
         <v>1.3</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D234" t="n">
-        <v>1.117566711180018</v>
+        <v>14.85167800881492</v>
       </c>
     </row>
     <row r="235">
@@ -3715,10 +3715,10 @@
         <v>1.3</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D235" t="n">
-        <v>0.1989775266321328</v>
+        <v>1.117566711180018</v>
       </c>
     </row>
     <row r="236">
@@ -3729,10 +3729,10 @@
         <v>1.3</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D236" t="n">
-        <v>11.99042792199484</v>
+        <v>0.1989775266321328</v>
       </c>
     </row>
     <row r="237">
@@ -3743,10 +3743,10 @@
         <v>1.3</v>
       </c>
       <c r="C237" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D237" t="n">
-        <v>17.8778675858085</v>
+        <v>11.99042792199484</v>
       </c>
     </row>
     <row r="238">
@@ -3757,10 +3757,10 @@
         <v>1.3</v>
       </c>
       <c r="C238" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D238" t="n">
-        <v>10.35218565937005</v>
+        <v>17.8778675858085</v>
       </c>
     </row>
     <row r="239">
@@ -3771,10 +3771,10 @@
         <v>1.3</v>
       </c>
       <c r="C239" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D239" t="n">
-        <v>14.2426594646236</v>
+        <v>10.35218565937005</v>
       </c>
     </row>
     <row r="240">
@@ -3782,13 +3782,13 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D240" t="n">
-        <v>-21.53664435089082</v>
+        <v>14.2426594646236</v>
       </c>
     </row>
     <row r="241">
@@ -3799,10 +3799,10 @@
         <v>1.4</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D241" t="n">
-        <v>9.328923873335238</v>
+        <v>-21.53664435089082</v>
       </c>
     </row>
     <row r="242">
@@ -3813,10 +3813,10 @@
         <v>1.4</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D242" t="n">
-        <v>10.10278720977517</v>
+        <v>9.328923873335238</v>
       </c>
     </row>
     <row r="243">
@@ -3827,10 +3827,10 @@
         <v>1.4</v>
       </c>
       <c r="C243" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D243" t="n">
-        <v>9.872864027314499</v>
+        <v>10.10278720977517</v>
       </c>
     </row>
     <row r="244">
@@ -3841,10 +3841,10 @@
         <v>1.4</v>
       </c>
       <c r="C244" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D244" t="n">
-        <v>32.99194919428567</v>
+        <v>9.872864027314499</v>
       </c>
     </row>
     <row r="245">
@@ -3855,10 +3855,10 @@
         <v>1.4</v>
       </c>
       <c r="C245" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D245" t="n">
-        <v>20.8988254865246</v>
+        <v>32.99194919428567</v>
       </c>
     </row>
     <row r="246">
@@ -3869,10 +3869,10 @@
         <v>1.4</v>
       </c>
       <c r="C246" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D246" t="n">
-        <v>21.02273262654837</v>
+        <v>20.8988254865246</v>
       </c>
     </row>
     <row r="247">
@@ -3880,13 +3880,13 @@
         <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="C247" t="n">
-        <v>-1</v>
+        <v>0.3</v>
       </c>
       <c r="D247" t="n">
-        <v>-28.86385928028418</v>
+        <v>21.02273262654837</v>
       </c>
     </row>
     <row r="248">
@@ -3897,10 +3897,10 @@
         <v>1.5</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="D248" t="n">
-        <v>-27.92286274706721</v>
+        <v>-28.86385928028418</v>
       </c>
     </row>
     <row r="249">
@@ -3911,10 +3911,10 @@
         <v>1.5</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="D249" t="n">
-        <v>2.689054849903094</v>
+        <v>-27.92286274706721</v>
       </c>
     </row>
     <row r="250">
@@ -3925,10 +3925,10 @@
         <v>1.5</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D250" t="n">
-        <v>-3.238398508380039</v>
+        <v>2.689054849903094</v>
       </c>
     </row>
     <row r="251">
@@ -3939,10 +3939,10 @@
         <v>1.5</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D251" t="n">
-        <v>-10.63284974670976</v>
+        <v>-3.238398508380039</v>
       </c>
     </row>
     <row r="252">
@@ -3953,10 +3953,10 @@
         <v>1.5</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D252" t="n">
-        <v>12.06314032941557</v>
+        <v>-10.63284974670976</v>
       </c>
     </row>
     <row r="253">
@@ -3967,10 +3967,10 @@
         <v>1.5</v>
       </c>
       <c r="C253" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D253" t="n">
-        <v>15.39130549839703</v>
+        <v>12.06314032941557</v>
       </c>
     </row>
     <row r="254">
@@ -3978,13 +3978,13 @@
         <v>252</v>
       </c>
       <c r="B254" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="D254" t="n">
-        <v>30.06161708518444</v>
+        <v>15.39130549839703</v>
       </c>
     </row>
     <row r="255">
@@ -3995,10 +3995,10 @@
         <v>1.6</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D255" t="n">
-        <v>0.7047925256585673</v>
+        <v>30.06161708518444</v>
       </c>
     </row>
     <row r="256">
@@ -4009,10 +4009,10 @@
         <v>1.6</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D256" t="n">
-        <v>10.63291564194945</v>
+        <v>0.7047925256585673</v>
       </c>
     </row>
     <row r="257">
@@ -4023,10 +4023,10 @@
         <v>1.6</v>
       </c>
       <c r="C257" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D257" t="n">
-        <v>13.41141054228502</v>
+        <v>10.63291564194945</v>
       </c>
     </row>
     <row r="258">
@@ -4037,10 +4037,10 @@
         <v>1.6</v>
       </c>
       <c r="C258" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D258" t="n">
-        <v>1.650019604266784</v>
+        <v>13.41141054228502</v>
       </c>
     </row>
     <row r="259">
@@ -4051,10 +4051,10 @@
         <v>1.6</v>
       </c>
       <c r="C259" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D259" t="n">
-        <v>28.22846781771771</v>
+        <v>1.650019604266784</v>
       </c>
     </row>
     <row r="260">
@@ -4062,13 +4062,13 @@
         <v>258</v>
       </c>
       <c r="B260" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="C260" t="n">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
       <c r="D260" t="n">
-        <v>-18.77733988349265</v>
+        <v>28.22846781771771</v>
       </c>
     </row>
     <row r="261">
@@ -4079,10 +4079,10 @@
         <v>1.7</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="D261" t="n">
-        <v>21.84579337894117</v>
+        <v>-18.77733988349265</v>
       </c>
     </row>
     <row r="262">
@@ -4093,10 +4093,10 @@
         <v>1.7</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="D262" t="n">
-        <v>-19.66556972907224</v>
+        <v>21.84579337894117</v>
       </c>
     </row>
     <row r="263">
@@ -4107,10 +4107,10 @@
         <v>1.7</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="D263" t="n">
-        <v>-3.553466162428487</v>
+        <v>-19.66556972907224</v>
       </c>
     </row>
     <row r="264">
@@ -4121,10 +4121,10 @@
         <v>1.7</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="D264" t="n">
-        <v>13.31529204441477</v>
+        <v>-3.553466162428487</v>
       </c>
     </row>
     <row r="265">
@@ -4135,10 +4135,10 @@
         <v>1.7</v>
       </c>
       <c r="C265" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D265" t="n">
-        <v>7.676380537871452</v>
+        <v>13.31529204441477</v>
       </c>
     </row>
     <row r="266">
@@ -4149,10 +4149,10 @@
         <v>1.7</v>
       </c>
       <c r="C266" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D266" t="n">
-        <v>20.33047799727875</v>
+        <v>7.676380537871452</v>
       </c>
     </row>
     <row r="267">
@@ -4163,10 +4163,10 @@
         <v>1.7</v>
       </c>
       <c r="C267" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D267" t="n">
-        <v>-3.787252747789704</v>
+        <v>20.33047799727875</v>
       </c>
     </row>
     <row r="268">
@@ -4174,13 +4174,13 @@
         <v>266</v>
       </c>
       <c r="B268" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="C268" t="n">
-        <v>-1.1</v>
+        <v>0.2</v>
       </c>
       <c r="D268" t="n">
-        <v>-23.29234065333936</v>
+        <v>-3.787252747789704</v>
       </c>
     </row>
     <row r="269">
@@ -4191,10 +4191,10 @@
         <v>1.8</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="D269" t="n">
-        <v>-3.974652769615716</v>
+        <v>-23.29234065333936</v>
       </c>
     </row>
     <row r="270">
@@ -4205,10 +4205,10 @@
         <v>1.8</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D270" t="n">
-        <v>4.340558528281924</v>
+        <v>-3.974652769615716</v>
       </c>
     </row>
     <row r="271">
@@ -4219,10 +4219,10 @@
         <v>1.8</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D271" t="n">
-        <v>3.842592511862401</v>
+        <v>4.340558528281924</v>
       </c>
     </row>
     <row r="272">
@@ -4233,10 +4233,10 @@
         <v>1.8</v>
       </c>
       <c r="C272" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D272" t="n">
-        <v>15.54694213528108</v>
+        <v>3.842592511862401</v>
       </c>
     </row>
     <row r="273">
@@ -4247,10 +4247,10 @@
         <v>1.8</v>
       </c>
       <c r="C273" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D273" t="n">
-        <v>2.175129839142603</v>
+        <v>15.54694213528108</v>
       </c>
     </row>
     <row r="274">
@@ -4261,10 +4261,10 @@
         <v>1.8</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D274" t="n">
-        <v>-1.034435819286472</v>
+        <v>2.175129839142603</v>
       </c>
     </row>
     <row r="275">
@@ -4272,13 +4272,13 @@
         <v>273</v>
       </c>
       <c r="B275" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.856228094308014</v>
+        <v>-1.034435819286472</v>
       </c>
     </row>
     <row r="276">
@@ -4289,10 +4289,10 @@
         <v>1.9</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D276" t="n">
-        <v>15.37696556690238</v>
+        <v>-2.856228094308014</v>
       </c>
     </row>
     <row r="277">
@@ -4303,10 +4303,10 @@
         <v>1.9</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D277" t="n">
-        <v>-13.45928790826484</v>
+        <v>15.37696556690238</v>
       </c>
     </row>
     <row r="278">
@@ -4317,10 +4317,10 @@
         <v>1.9</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D278" t="n">
-        <v>12.72257206711829</v>
+        <v>-13.45928790826484</v>
       </c>
     </row>
     <row r="279">
@@ -4328,13 +4328,13 @@
         <v>277</v>
       </c>
       <c r="B279" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="D279" t="n">
-        <v>13.78724913351632</v>
+        <v>12.72257206711829</v>
       </c>
     </row>
     <row r="280">
@@ -4345,10 +4345,10 @@
         <v>2</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="D280" t="n">
-        <v>18.72574927547594</v>
+        <v>13.78724913351632</v>
       </c>
     </row>
     <row r="281">
@@ -4359,10 +4359,10 @@
         <v>2</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D281" t="n">
-        <v>21.11336312725731</v>
+        <v>18.72574927547594</v>
       </c>
     </row>
     <row r="282">
@@ -4373,10 +4373,10 @@
         <v>2</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D282" t="n">
-        <v>17.39246112275586</v>
+        <v>21.11336312725731</v>
       </c>
     </row>
     <row r="283">
@@ -4387,10 +4387,10 @@
         <v>2</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D283" t="n">
-        <v>17.00766010495393</v>
+        <v>17.39246112275586</v>
       </c>
     </row>
     <row r="284">
@@ -4401,10 +4401,10 @@
         <v>2</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D284" t="n">
-        <v>-9.280344533884243</v>
+        <v>17.00766010495393</v>
       </c>
     </row>
     <row r="285">
@@ -4415,10 +4415,10 @@
         <v>2</v>
       </c>
       <c r="C285" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="D285" t="n">
-        <v>16.43776248864852</v>
+        <v>-9.280344533884243</v>
       </c>
     </row>
     <row r="286">
@@ -4426,13 +4426,13 @@
         <v>284</v>
       </c>
       <c r="B286" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D286" t="n">
-        <v>8.212539103417916</v>
+        <v>16.43776248864852</v>
       </c>
     </row>
     <row r="287">
@@ -4443,10 +4443,10 @@
         <v>2.1</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="D287" t="n">
-        <v>23.56968332972611</v>
+        <v>8.212539103417916</v>
       </c>
     </row>
     <row r="288">
@@ -4457,10 +4457,10 @@
         <v>2.1</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D288" t="n">
-        <v>17.61012028400106</v>
+        <v>23.56968332972611</v>
       </c>
     </row>
     <row r="289">
@@ -4471,10 +4471,10 @@
         <v>2.1</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D289" t="n">
-        <v>-13.79042182501424</v>
+        <v>17.61012028400106</v>
       </c>
     </row>
     <row r="290">
@@ -4485,10 +4485,10 @@
         <v>2.1</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D290" t="n">
-        <v>-6.992659577669663</v>
+        <v>-13.79042182501424</v>
       </c>
     </row>
     <row r="291">
@@ -4499,10 +4499,10 @@
         <v>2.1</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D291" t="n">
-        <v>26.48235627698286</v>
+        <v>-6.992659577669663</v>
       </c>
     </row>
     <row r="292">
@@ -4513,10 +4513,10 @@
         <v>2.1</v>
       </c>
       <c r="C292" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D292" t="n">
-        <v>-14.1103932017413</v>
+        <v>26.48235627698286</v>
       </c>
     </row>
     <row r="293">
@@ -4527,10 +4527,10 @@
         <v>2.1</v>
       </c>
       <c r="C293" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>9.425450655310886</v>
+        <v>-14.1103932017413</v>
       </c>
     </row>
     <row r="294">
@@ -4538,13 +4538,13 @@
         <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="D294" t="n">
-        <v>26.9891539335585</v>
+        <v>9.425450655310886</v>
       </c>
     </row>
     <row r="295">
@@ -4555,10 +4555,10 @@
         <v>2.2</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="D295" t="n">
-        <v>15.2980820925372</v>
+        <v>26.9891539335585</v>
       </c>
     </row>
     <row r="296">
@@ -4569,10 +4569,10 @@
         <v>2.2</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D296" t="n">
-        <v>9.381257126875875</v>
+        <v>15.2980820925372</v>
       </c>
     </row>
     <row r="297">
@@ -4583,10 +4583,10 @@
         <v>2.2</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D297" t="n">
-        <v>-4.878460416933283</v>
+        <v>9.381257126875875</v>
       </c>
     </row>
     <row r="298">
@@ -4597,10 +4597,10 @@
         <v>2.2</v>
       </c>
       <c r="C298" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="D298" t="n">
-        <v>-4.202882644640982</v>
+        <v>-4.878460416933283</v>
       </c>
     </row>
     <row r="299">
@@ -4608,13 +4608,13 @@
         <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="D299" t="n">
-        <v>30.23578444332056</v>
+        <v>-4.202882644640982</v>
       </c>
     </row>
     <row r="300">
@@ -4625,10 +4625,10 @@
         <v>2.3</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D300" t="n">
-        <v>-20.19643865448743</v>
+        <v>30.23578444332056</v>
       </c>
     </row>
     <row r="301">
@@ -4639,10 +4639,10 @@
         <v>2.3</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D301" t="n">
-        <v>-34.16261962418616</v>
+        <v>-20.19643865448743</v>
       </c>
     </row>
     <row r="302">
@@ -4650,13 +4650,13 @@
         <v>300</v>
       </c>
       <c r="B302" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="C302" t="n">
         <v>-0.1</v>
       </c>
       <c r="D302" t="n">
-        <v>-32.9675118294535</v>
+        <v>-34.16261962418616</v>
       </c>
     </row>
     <row r="303">
@@ -4667,10 +4667,10 @@
         <v>2.4</v>
       </c>
       <c r="C303" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D303" t="n">
-        <v>-9.091828309751271</v>
+        <v>-32.9675118294535</v>
       </c>
     </row>
     <row r="304">
@@ -4678,12 +4678,26 @@
         <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
       </c>
       <c r="D304" t="n">
+        <v>-9.091828309751271</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>303</v>
+      </c>
+      <c r="B305" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0</v>
+      </c>
+      <c r="D305" t="n">
         <v>-4.236294380286648</v>
       </c>
     </row>
@@ -4968,13 +4982,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85551A00-98F1-4CA9-B913-D351805A1100}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33D2ACFD-4858-4A0E-BB90-6074B6E8B8A2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92BA2FB8-6CB8-4A94-9BDF-4572E9BE5007}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3832CD4F-AB17-49F6-9926-34BD9958807E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B945B8-1819-491F-B945-AA40470B8FAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3891EA5D-F741-4189-A1BB-9B9B3CBDDD7C}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_grouped.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_TESTCONTOUR_grouped.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D305"/>
+  <dimension ref="A1:D306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1422,7 +1422,7 @@
         <v>0.1</v>
       </c>
       <c r="D71" t="n">
-        <v>11.24801113340989</v>
+        <v>16.03067551301344</v>
       </c>
     </row>
     <row r="72">
@@ -1430,13 +1430,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D72" t="n">
-        <v>12.01511145919841</v>
+        <v>47.22484755237713</v>
       </c>
     </row>
     <row r="73">
@@ -1447,10 +1447,10 @@
         <v>-1.1</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>20.21312670289172</v>
+        <v>12.01511145919841</v>
       </c>
     </row>
     <row r="74">
@@ -1461,10 +1461,10 @@
         <v>-1.1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D74" t="n">
-        <v>9.340313376676379</v>
+        <v>20.21312670289172</v>
       </c>
     </row>
     <row r="75">
@@ -1475,10 +1475,10 @@
         <v>-1.1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D75" t="n">
-        <v>11.49238646524473</v>
+        <v>9.340313376676379</v>
       </c>
     </row>
     <row r="76">
@@ -1486,13 +1486,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D76" t="n">
-        <v>-10.10953812013922</v>
+        <v>11.49238646524473</v>
       </c>
     </row>
     <row r="77">
@@ -1503,10 +1503,10 @@
         <v>-1</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D77" t="n">
-        <v>-5.92621924840283</v>
+        <v>-10.10953812013922</v>
       </c>
     </row>
     <row r="78">
@@ -1517,10 +1517,10 @@
         <v>-1</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="D78" t="n">
-        <v>11.59621764602354</v>
+        <v>-5.92621924840283</v>
       </c>
     </row>
     <row r="79">
@@ -1531,10 +1531,10 @@
         <v>-1</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D79" t="n">
-        <v>20.15641168256447</v>
+        <v>11.59621764602354</v>
       </c>
     </row>
     <row r="80">
@@ -1545,10 +1545,10 @@
         <v>-1</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D80" t="n">
-        <v>7.562179536973295</v>
+        <v>20.15641168256447</v>
       </c>
     </row>
     <row r="81">
@@ -1556,13 +1556,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="D81" t="n">
-        <v>17.31903482350436</v>
+        <v>7.562179536973295</v>
       </c>
     </row>
     <row r="82">
@@ -1573,10 +1573,10 @@
         <v>-0.9</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D82" t="n">
-        <v>19.5534934785758</v>
+        <v>17.31903482350436</v>
       </c>
     </row>
     <row r="83">
@@ -1587,10 +1587,10 @@
         <v>-0.9</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D83" t="n">
-        <v>9.150304569791889</v>
+        <v>19.5534934785758</v>
       </c>
     </row>
     <row r="84">
@@ -1601,10 +1601,10 @@
         <v>-0.9</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D84" t="n">
-        <v>17.13330513789267</v>
+        <v>9.150304569791889</v>
       </c>
     </row>
     <row r="85">
@@ -1615,10 +1615,10 @@
         <v>-0.9</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>10.01856323137027</v>
+        <v>17.13330513789267</v>
       </c>
     </row>
     <row r="86">
@@ -1629,10 +1629,10 @@
         <v>-0.9</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D86" t="n">
-        <v>25.84651511002527</v>
+        <v>10.01856323137027</v>
       </c>
     </row>
     <row r="87">
@@ -1643,10 +1643,10 @@
         <v>-0.9</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D87" t="n">
-        <v>2.775317121015397</v>
+        <v>25.84651511002527</v>
       </c>
     </row>
     <row r="88">
@@ -1657,10 +1657,10 @@
         <v>-0.9</v>
       </c>
       <c r="C88" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D88" t="n">
-        <v>8.010909403402721</v>
+        <v>2.775317121015397</v>
       </c>
     </row>
     <row r="89">
@@ -1668,13 +1668,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D89" t="n">
-        <v>32.49688209597053</v>
+        <v>8.010909403402721</v>
       </c>
     </row>
     <row r="90">
@@ -1685,10 +1685,10 @@
         <v>-0.8</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D90" t="n">
-        <v>-4.245257729307916</v>
+        <v>32.49688209597053</v>
       </c>
     </row>
     <row r="91">
@@ -1699,10 +1699,10 @@
         <v>-0.8</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D91" t="n">
-        <v>16.59444445072643</v>
+        <v>-4.245257729307916</v>
       </c>
     </row>
     <row r="92">
@@ -1713,10 +1713,10 @@
         <v>-0.8</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D92" t="n">
-        <v>16.36696596059325</v>
+        <v>16.59444445072643</v>
       </c>
     </row>
     <row r="93">
@@ -1727,10 +1727,10 @@
         <v>-0.8</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>7.359221554684029</v>
+        <v>16.36696596059325</v>
       </c>
     </row>
     <row r="94">
@@ -1741,10 +1741,10 @@
         <v>-0.8</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D94" t="n">
-        <v>7.447912052149815</v>
+        <v>7.359221554684029</v>
       </c>
     </row>
     <row r="95">
@@ -1755,10 +1755,10 @@
         <v>-0.8</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D95" t="n">
-        <v>13.5225535827757</v>
+        <v>7.447912052149815</v>
       </c>
     </row>
     <row r="96">
@@ -1769,10 +1769,10 @@
         <v>-0.8</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D96" t="n">
-        <v>3.760721630210839</v>
+        <v>13.5225535827757</v>
       </c>
     </row>
     <row r="97">
@@ -1780,13 +1780,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D97" t="n">
-        <v>-3.295103945896905</v>
+        <v>3.760721630210839</v>
       </c>
     </row>
     <row r="98">
@@ -1797,10 +1797,10 @@
         <v>-0.7</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D98" t="n">
-        <v>8.854013381408961</v>
+        <v>-3.295103945896905</v>
       </c>
     </row>
     <row r="99">
@@ -1811,10 +1811,10 @@
         <v>-0.7</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D99" t="n">
-        <v>10.10934734452611</v>
+        <v>8.854013381408961</v>
       </c>
     </row>
     <row r="100">
@@ -1825,10 +1825,10 @@
         <v>-0.7</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>12.45005147499743</v>
+        <v>10.10934734452611</v>
       </c>
     </row>
     <row r="101">
@@ -1839,10 +1839,10 @@
         <v>-0.7</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D101" t="n">
-        <v>28.25584185685916</v>
+        <v>12.45005147499743</v>
       </c>
     </row>
     <row r="102">
@@ -1850,13 +1850,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D102" t="n">
-        <v>38.40703381314563</v>
+        <v>28.25584185685916</v>
       </c>
     </row>
     <row r="103">
@@ -1867,10 +1867,10 @@
         <v>-0.6</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="D103" t="n">
-        <v>9.610479570395958</v>
+        <v>38.40703381314563</v>
       </c>
     </row>
     <row r="104">
@@ -1881,10 +1881,10 @@
         <v>-0.6</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D104" t="n">
-        <v>6.257388578121698</v>
+        <v>9.610479570395958</v>
       </c>
     </row>
     <row r="105">
@@ -1895,10 +1895,10 @@
         <v>-0.6</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D105" t="n">
-        <v>9.914194347595121</v>
+        <v>6.257388578121698</v>
       </c>
     </row>
     <row r="106">
@@ -1909,10 +1909,10 @@
         <v>-0.6</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D106" t="n">
-        <v>15.82025254968401</v>
+        <v>9.914194347595121</v>
       </c>
     </row>
     <row r="107">
@@ -1923,10 +1923,10 @@
         <v>-0.6</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>16.57553971333769</v>
+        <v>15.82025254968401</v>
       </c>
     </row>
     <row r="108">
@@ -1937,10 +1937,10 @@
         <v>-0.6</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D108" t="n">
-        <v>6.012699659193837</v>
+        <v>16.57553971333769</v>
       </c>
     </row>
     <row r="109">
@@ -1951,10 +1951,10 @@
         <v>-0.6</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D109" t="n">
-        <v>22.56158446324479</v>
+        <v>6.012699659193837</v>
       </c>
     </row>
     <row r="110">
@@ -1965,10 +1965,10 @@
         <v>-0.6</v>
       </c>
       <c r="C110" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D110" t="n">
-        <v>27.63714927361014</v>
+        <v>22.56158446324479</v>
       </c>
     </row>
     <row r="111">
@@ -1976,13 +1976,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D111" t="n">
-        <v>8.898772015691709</v>
+        <v>27.63714927361014</v>
       </c>
     </row>
     <row r="112">
@@ -1993,10 +1993,10 @@
         <v>-0.5</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D112" t="n">
-        <v>5.406472437959754</v>
+        <v>8.898772015691709</v>
       </c>
     </row>
     <row r="113">
@@ -2007,10 +2007,10 @@
         <v>-0.5</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D113" t="n">
-        <v>20.89983643824696</v>
+        <v>5.406472437959754</v>
       </c>
     </row>
     <row r="114">
@@ -2021,10 +2021,10 @@
         <v>-0.5</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D114" t="n">
-        <v>22.71840750732937</v>
+        <v>20.89983643824696</v>
       </c>
     </row>
     <row r="115">
@@ -2035,10 +2035,10 @@
         <v>-0.5</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>20.73020246429007</v>
+        <v>22.71840750732937</v>
       </c>
     </row>
     <row r="116">
@@ -2049,10 +2049,10 @@
         <v>-0.5</v>
       </c>
       <c r="C116" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D116" t="n">
-        <v>14.12591159576888</v>
+        <v>20.73020246429007</v>
       </c>
     </row>
     <row r="117">
@@ -2063,10 +2063,10 @@
         <v>-0.5</v>
       </c>
       <c r="C117" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D117" t="n">
-        <v>13.35039006591945</v>
+        <v>14.12591159576888</v>
       </c>
     </row>
     <row r="118">
@@ -2077,10 +2077,10 @@
         <v>-0.5</v>
       </c>
       <c r="C118" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D118" t="n">
-        <v>21.84679967196988</v>
+        <v>13.35039006591945</v>
       </c>
     </row>
     <row r="119">
@@ -2088,13 +2088,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D119" t="n">
-        <v>-3.586847936385662</v>
+        <v>21.84679967196988</v>
       </c>
     </row>
     <row r="120">
@@ -2105,10 +2105,10 @@
         <v>-0.4</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D120" t="n">
-        <v>22.30386193208223</v>
+        <v>-3.586847936385662</v>
       </c>
     </row>
     <row r="121">
@@ -2119,10 +2119,10 @@
         <v>-0.4</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D121" t="n">
-        <v>15.05120190401821</v>
+        <v>22.30386193208223</v>
       </c>
     </row>
     <row r="122">
@@ -2133,10 +2133,10 @@
         <v>-0.4</v>
       </c>
       <c r="C122" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>15.44754024392076</v>
+        <v>15.05120190401821</v>
       </c>
     </row>
     <row r="123">
@@ -2147,10 +2147,10 @@
         <v>-0.4</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D123" t="n">
-        <v>22.10829809189676</v>
+        <v>15.44754024392076</v>
       </c>
     </row>
     <row r="124">
@@ -2161,10 +2161,10 @@
         <v>-0.4</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D124" t="n">
-        <v>19.72421963246074</v>
+        <v>22.10829809189676</v>
       </c>
     </row>
     <row r="125">
@@ -2175,10 +2175,10 @@
         <v>-0.4</v>
       </c>
       <c r="C125" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D125" t="n">
-        <v>16.50016608436669</v>
+        <v>19.72421963246074</v>
       </c>
     </row>
     <row r="126">
@@ -2186,13 +2186,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D126" t="n">
-        <v>35.31524330966344</v>
+        <v>16.50016608436669</v>
       </c>
     </row>
     <row r="127">
@@ -2203,10 +2203,10 @@
         <v>-0.3</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D127" t="n">
-        <v>4.343892684273276</v>
+        <v>35.31524330966344</v>
       </c>
     </row>
     <row r="128">
@@ -2217,10 +2217,10 @@
         <v>-0.3</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D128" t="n">
-        <v>-3.18058767263614</v>
+        <v>4.343892684273276</v>
       </c>
     </row>
     <row r="129">
@@ -2231,10 +2231,10 @@
         <v>-0.3</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D129" t="n">
-        <v>20.54730769394918</v>
+        <v>-3.18058767263614</v>
       </c>
     </row>
     <row r="130">
@@ -2245,10 +2245,10 @@
         <v>-0.3</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>8.707759284382448</v>
+        <v>20.54730769394918</v>
       </c>
     </row>
     <row r="131">
@@ -2259,10 +2259,10 @@
         <v>-0.3</v>
       </c>
       <c r="C131" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D131" t="n">
-        <v>25.2898350113473</v>
+        <v>8.707759284382448</v>
       </c>
     </row>
     <row r="132">
@@ -2273,10 +2273,10 @@
         <v>-0.3</v>
       </c>
       <c r="C132" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D132" t="n">
-        <v>11.26840126060807</v>
+        <v>25.2898350113473</v>
       </c>
     </row>
     <row r="133">
@@ -2284,13 +2284,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D133" t="n">
-        <v>13.52806940157711</v>
+        <v>11.26840126060807</v>
       </c>
     </row>
     <row r="134">
@@ -2301,10 +2301,10 @@
         <v>-0.2</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="D134" t="n">
-        <v>24.74071716269537</v>
+        <v>13.52806940157711</v>
       </c>
     </row>
     <row r="135">
@@ -2315,10 +2315,10 @@
         <v>-0.2</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D135" t="n">
-        <v>13.99908566516049</v>
+        <v>24.74071716269537</v>
       </c>
     </row>
     <row r="136">
@@ -2329,10 +2329,10 @@
         <v>-0.2</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>13.0840098349689</v>
+        <v>13.99908566516049</v>
       </c>
     </row>
     <row r="137">
@@ -2343,10 +2343,10 @@
         <v>-0.2</v>
       </c>
       <c r="C137" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D137" t="n">
-        <v>29.40056985998893</v>
+        <v>13.0840098349689</v>
       </c>
     </row>
     <row r="138">
@@ -2357,10 +2357,10 @@
         <v>-0.2</v>
       </c>
       <c r="C138" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D138" t="n">
-        <v>11.99860786056441</v>
+        <v>29.40056985998893</v>
       </c>
     </row>
     <row r="139">
@@ -2371,10 +2371,10 @@
         <v>-0.2</v>
       </c>
       <c r="C139" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="D139" t="n">
-        <v>11.62716768865067</v>
+        <v>11.99860786056441</v>
       </c>
     </row>
     <row r="140">
@@ -2382,13 +2382,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D140" t="n">
-        <v>38.03317170768623</v>
+        <v>11.62716768865067</v>
       </c>
     </row>
     <row r="141">
@@ -2399,10 +2399,10 @@
         <v>-0.1</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="D141" t="n">
-        <v>26.13664646256055</v>
+        <v>38.03317170768623</v>
       </c>
     </row>
     <row r="142">
@@ -2413,10 +2413,10 @@
         <v>-0.1</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="D142" t="n">
-        <v>21.49294428478238</v>
+        <v>26.13664646256055</v>
       </c>
     </row>
     <row r="143">
@@ -2427,10 +2427,10 @@
         <v>-0.1</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D143" t="n">
-        <v>10.39918451703468</v>
+        <v>21.49294428478238</v>
       </c>
     </row>
     <row r="144">
@@ -2441,10 +2441,10 @@
         <v>-0.1</v>
       </c>
       <c r="C144" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>9.107548918683161</v>
+        <v>10.39918451703468</v>
       </c>
     </row>
     <row r="145">
@@ -2455,10 +2455,10 @@
         <v>-0.1</v>
       </c>
       <c r="C145" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D145" t="n">
-        <v>11.86945294864077</v>
+        <v>9.107548918683161</v>
       </c>
     </row>
     <row r="146">
@@ -2469,10 +2469,10 @@
         <v>-0.1</v>
       </c>
       <c r="C146" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D146" t="n">
-        <v>29.40242982712884</v>
+        <v>11.86945294864077</v>
       </c>
     </row>
     <row r="147">
@@ -2483,10 +2483,10 @@
         <v>-0.1</v>
       </c>
       <c r="C147" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D147" t="n">
-        <v>-6.304089349534692</v>
+        <v>29.40242982712884</v>
       </c>
     </row>
     <row r="148">
@@ -2494,13 +2494,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D148" t="n">
-        <v>12.887136334722</v>
+        <v>-6.304089349534692</v>
       </c>
     </row>
     <row r="149">
@@ -2511,10 +2511,10 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D149" t="n">
-        <v>15.24618485365237</v>
+        <v>12.887136334722</v>
       </c>
     </row>
     <row r="150">
@@ -2525,10 +2525,10 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>15.2203514657723</v>
+        <v>15.24618485365237</v>
       </c>
     </row>
     <row r="151">
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D151" t="n">
-        <v>16.6414844089368</v>
+        <v>15.2203514657723</v>
       </c>
     </row>
     <row r="152">
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D152" t="n">
-        <v>12.34534228433971</v>
+        <v>16.6414844089368</v>
       </c>
     </row>
     <row r="153">
@@ -2564,13 +2564,13 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>-1.8</v>
+        <v>0.3</v>
       </c>
       <c r="D153" t="n">
-        <v>20.65558253568762</v>
+        <v>12.34534228433971</v>
       </c>
     </row>
     <row r="154">
@@ -2581,10 +2581,10 @@
         <v>0.1</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="D154" t="n">
-        <v>21.93524042214195</v>
+        <v>20.65558253568762</v>
       </c>
     </row>
     <row r="155">
@@ -2595,10 +2595,10 @@
         <v>0.1</v>
       </c>
       <c r="C155" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>12.95881016986827</v>
+        <v>21.93524042214195</v>
       </c>
     </row>
     <row r="156">
@@ -2609,10 +2609,10 @@
         <v>0.1</v>
       </c>
       <c r="C156" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D156" t="n">
-        <v>20.51006817005711</v>
+        <v>12.95881016986827</v>
       </c>
     </row>
     <row r="157">
@@ -2620,13 +2620,13 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C157" t="n">
         <v>0.2</v>
       </c>
-      <c r="C157" t="n">
-        <v>-0.8</v>
-      </c>
       <c r="D157" t="n">
-        <v>8.675499305158517</v>
+        <v>20.51006817005711</v>
       </c>
     </row>
     <row r="158">
@@ -2637,10 +2637,10 @@
         <v>0.2</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="D158" t="n">
-        <v>11.73274125115487</v>
+        <v>8.675499305158517</v>
       </c>
     </row>
     <row r="159">
@@ -2651,10 +2651,10 @@
         <v>0.2</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D159" t="n">
-        <v>-10.48272761205174</v>
+        <v>11.73274125115487</v>
       </c>
     </row>
     <row r="160">
@@ -2665,10 +2665,10 @@
         <v>0.2</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D160" t="n">
-        <v>-4.102810132891062</v>
+        <v>-10.48272761205174</v>
       </c>
     </row>
     <row r="161">
@@ -2679,10 +2679,10 @@
         <v>0.2</v>
       </c>
       <c r="C161" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="D161" t="n">
-        <v>22.24487931933098</v>
+        <v>-4.102810132891062</v>
       </c>
     </row>
     <row r="162">
@@ -2693,10 +2693,10 @@
         <v>0.2</v>
       </c>
       <c r="C162" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D162" t="n">
-        <v>9.03314495772889</v>
+        <v>22.24487931933098</v>
       </c>
     </row>
     <row r="163">
@@ -2707,10 +2707,10 @@
         <v>0.2</v>
       </c>
       <c r="C163" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D163" t="n">
-        <v>12.89231662866284</v>
+        <v>9.03314495772889</v>
       </c>
     </row>
     <row r="164">
@@ -2718,13 +2718,13 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C164" t="n">
         <v>0.3</v>
       </c>
-      <c r="C164" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="D164" t="n">
-        <v>34.3200087534147</v>
+        <v>12.89231662866284</v>
       </c>
     </row>
     <row r="165">
@@ -2735,10 +2735,10 @@
         <v>0.3</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="D165" t="n">
-        <v>-7.220868045776685</v>
+        <v>34.3200087534147</v>
       </c>
     </row>
     <row r="166">
@@ -2749,10 +2749,10 @@
         <v>0.3</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D166" t="n">
-        <v>22.68607581675329</v>
+        <v>-7.220868045776685</v>
       </c>
     </row>
     <row r="167">
@@ -2763,10 +2763,10 @@
         <v>0.3</v>
       </c>
       <c r="C167" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>17.25238272973596</v>
+        <v>22.68607581675329</v>
       </c>
     </row>
     <row r="168">
@@ -2777,10 +2777,10 @@
         <v>0.3</v>
       </c>
       <c r="C168" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D168" t="n">
-        <v>13.65983021502197</v>
+        <v>17.25238272973596</v>
       </c>
     </row>
     <row r="169">
@@ -2788,13 +2788,13 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C169" t="n">
         <v>0.4</v>
       </c>
-      <c r="C169" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="D169" t="n">
-        <v>16.24970313980212</v>
+        <v>13.65983021502197</v>
       </c>
     </row>
     <row r="170">
@@ -2805,10 +2805,10 @@
         <v>0.4</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="D170" t="n">
-        <v>8.724666083835872</v>
+        <v>16.24970313980212</v>
       </c>
     </row>
     <row r="171">
@@ -2819,10 +2819,10 @@
         <v>0.4</v>
       </c>
       <c r="C171" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D171" t="n">
-        <v>14.59002027965239</v>
+        <v>8.724666083835872</v>
       </c>
     </row>
     <row r="172">
@@ -2833,10 +2833,10 @@
         <v>0.4</v>
       </c>
       <c r="C172" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D172" t="n">
-        <v>7.080409836316237</v>
+        <v>14.59002027965239</v>
       </c>
     </row>
     <row r="173">
@@ -2844,13 +2844,13 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D173" t="n">
-        <v>-35.69907125330158</v>
+        <v>7.080409836316237</v>
       </c>
     </row>
     <row r="174">
@@ -2861,10 +2861,10 @@
         <v>0.5</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D174" t="n">
-        <v>-2.528977258676479</v>
+        <v>-35.69907125330158</v>
       </c>
     </row>
     <row r="175">
@@ -2875,10 +2875,10 @@
         <v>0.5</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D175" t="n">
-        <v>8.959448245783976</v>
+        <v>-2.528977258676479</v>
       </c>
     </row>
     <row r="176">
@@ -2889,10 +2889,10 @@
         <v>0.5</v>
       </c>
       <c r="C176" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>4.562753904953365</v>
+        <v>8.959448245783976</v>
       </c>
     </row>
     <row r="177">
@@ -2903,10 +2903,10 @@
         <v>0.5</v>
       </c>
       <c r="C177" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D177" t="n">
-        <v>16.85459832183653</v>
+        <v>4.562753904953365</v>
       </c>
     </row>
     <row r="178">
@@ -2917,10 +2917,10 @@
         <v>0.5</v>
       </c>
       <c r="C178" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D178" t="n">
-        <v>11.30381646904931</v>
+        <v>16.85459832183653</v>
       </c>
     </row>
     <row r="179">
@@ -2931,10 +2931,10 @@
         <v>0.5</v>
       </c>
       <c r="C179" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D179" t="n">
-        <v>-6.332076215563898</v>
+        <v>11.30381646904931</v>
       </c>
     </row>
     <row r="180">
@@ -2942,13 +2942,13 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D180" t="n">
-        <v>23.31763820152588</v>
+        <v>-6.332076215563898</v>
       </c>
     </row>
     <row r="181">
@@ -2959,10 +2959,10 @@
         <v>0.6</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D181" t="n">
-        <v>9.003359893565621</v>
+        <v>23.31763820152588</v>
       </c>
     </row>
     <row r="182">
@@ -2973,10 +2973,10 @@
         <v>0.6</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="D182" t="n">
-        <v>17.68825690676043</v>
+        <v>9.003359893565621</v>
       </c>
     </row>
     <row r="183">
@@ -2987,10 +2987,10 @@
         <v>0.6</v>
       </c>
       <c r="C183" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D183" t="n">
-        <v>6.236663804781623</v>
+        <v>17.68825690676043</v>
       </c>
     </row>
     <row r="184">
@@ -3001,10 +3001,10 @@
         <v>0.6</v>
       </c>
       <c r="C184" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>26.46960405199754</v>
+        <v>6.236663804781623</v>
       </c>
     </row>
     <row r="185">
@@ -3015,10 +3015,10 @@
         <v>0.6</v>
       </c>
       <c r="C185" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D185" t="n">
-        <v>20.20773014373248</v>
+        <v>26.46960405199754</v>
       </c>
     </row>
     <row r="186">
@@ -3029,10 +3029,10 @@
         <v>0.6</v>
       </c>
       <c r="C186" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D186" t="n">
-        <v>15.44676767833113</v>
+        <v>20.20773014373248</v>
       </c>
     </row>
     <row r="187">
@@ -3040,13 +3040,13 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D187" t="n">
-        <v>17.86620487654922</v>
+        <v>15.44676767833113</v>
       </c>
     </row>
     <row r="188">
@@ -3057,10 +3057,10 @@
         <v>0.7</v>
       </c>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D188" t="n">
-        <v>-3.145568089499773</v>
+        <v>17.86620487654922</v>
       </c>
     </row>
     <row r="189">
@@ -3071,10 +3071,10 @@
         <v>0.7</v>
       </c>
       <c r="C189" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>24.39952726530608</v>
+        <v>-3.145568089499773</v>
       </c>
     </row>
     <row r="190">
@@ -3085,10 +3085,10 @@
         <v>0.7</v>
       </c>
       <c r="C190" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D190" t="n">
-        <v>22.14445093028229</v>
+        <v>24.39952726530608</v>
       </c>
     </row>
     <row r="191">
@@ -3099,10 +3099,10 @@
         <v>0.7</v>
       </c>
       <c r="C191" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D191" t="n">
-        <v>-8.539851952354704</v>
+        <v>22.14445093028229</v>
       </c>
     </row>
     <row r="192">
@@ -3110,13 +3110,13 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D192" t="n">
-        <v>-36.32794889204803</v>
+        <v>-8.539851952354704</v>
       </c>
     </row>
     <row r="193">
@@ -3127,10 +3127,10 @@
         <v>0.8</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D193" t="n">
-        <v>-40.90711089487865</v>
+        <v>-36.32794889204803</v>
       </c>
     </row>
     <row r="194">
@@ -3141,10 +3141,10 @@
         <v>0.8</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="D194" t="n">
-        <v>-13.37967884285289</v>
+        <v>-40.90711089487865</v>
       </c>
     </row>
     <row r="195">
@@ -3155,10 +3155,10 @@
         <v>0.8</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D195" t="n">
-        <v>2.42507817976994</v>
+        <v>-13.37967884285289</v>
       </c>
     </row>
     <row r="196">
@@ -3169,10 +3169,10 @@
         <v>0.8</v>
       </c>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D196" t="n">
-        <v>16.79126653912467</v>
+        <v>2.42507817976994</v>
       </c>
     </row>
     <row r="197">
@@ -3183,10 +3183,10 @@
         <v>0.8</v>
       </c>
       <c r="C197" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>18.84562481075803</v>
+        <v>16.79126653912467</v>
       </c>
     </row>
     <row r="198">
@@ -3197,10 +3197,10 @@
         <v>0.8</v>
       </c>
       <c r="C198" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D198" t="n">
-        <v>1.630749191837651</v>
+        <v>18.84562481075803</v>
       </c>
     </row>
     <row r="199">
@@ -3208,13 +3208,13 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D199" t="n">
-        <v>16.96832641513663</v>
+        <v>1.630749191837651</v>
       </c>
     </row>
     <row r="200">
@@ -3225,10 +3225,10 @@
         <v>0.9</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="D200" t="n">
-        <v>9.667322606019651</v>
+        <v>16.96832641513663</v>
       </c>
     </row>
     <row r="201">
@@ -3239,10 +3239,10 @@
         <v>0.9</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D201" t="n">
-        <v>16.93508581405908</v>
+        <v>9.667322606019651</v>
       </c>
     </row>
     <row r="202">
@@ -3253,10 +3253,10 @@
         <v>0.9</v>
       </c>
       <c r="C202" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>11.25068766258671</v>
+        <v>16.93508581405908</v>
       </c>
     </row>
     <row r="203">
@@ -3267,10 +3267,10 @@
         <v>0.9</v>
       </c>
       <c r="C203" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D203" t="n">
-        <v>21.68034025664982</v>
+        <v>11.25068766258671</v>
       </c>
     </row>
     <row r="204">
@@ -3281,10 +3281,10 @@
         <v>0.9</v>
       </c>
       <c r="C204" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D204" t="n">
-        <v>10.01949013751486</v>
+        <v>21.68034025664982</v>
       </c>
     </row>
     <row r="205">
@@ -3292,13 +3292,13 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.9</v>
+        <v>0.3</v>
       </c>
       <c r="D205" t="n">
-        <v>9.338123687716626</v>
+        <v>10.01949013751486</v>
       </c>
     </row>
     <row r="206">
@@ -3309,10 +3309,10 @@
         <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="D206" t="n">
-        <v>-38.98932234183646</v>
+        <v>9.338123687716626</v>
       </c>
     </row>
     <row r="207">
@@ -3323,10 +3323,10 @@
         <v>1</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D207" t="n">
-        <v>-4.049027247638014</v>
+        <v>-38.98932234183646</v>
       </c>
     </row>
     <row r="208">
@@ -3337,10 +3337,10 @@
         <v>1</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D208" t="n">
-        <v>11.28699341118687</v>
+        <v>-4.049027247638014</v>
       </c>
     </row>
     <row r="209">
@@ -3351,10 +3351,10 @@
         <v>1</v>
       </c>
       <c r="C209" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D209" t="n">
-        <v>16.41663227719419</v>
+        <v>11.28699341118687</v>
       </c>
     </row>
     <row r="210">
@@ -3365,10 +3365,10 @@
         <v>1</v>
       </c>
       <c r="C210" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>26.94742380345686</v>
+        <v>16.41663227719419</v>
       </c>
     </row>
     <row r="211">
@@ -3379,10 +3379,10 @@
         <v>1</v>
       </c>
       <c r="C211" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D211" t="n">
-        <v>6.875770128986824</v>
+        <v>26.94742380345686</v>
       </c>
     </row>
     <row r="212">
@@ -3393,10 +3393,10 @@
         <v>1</v>
       </c>
       <c r="C212" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D212" t="n">
-        <v>-1.835302430313079</v>
+        <v>6.875770128986824</v>
       </c>
     </row>
     <row r="213">
@@ -3404,13 +3404,13 @@
         <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.9</v>
+        <v>0.3</v>
       </c>
       <c r="D213" t="n">
-        <v>-11.52350378740865</v>
+        <v>-1.835302430313079</v>
       </c>
     </row>
     <row r="214">
@@ -3421,10 +3421,10 @@
         <v>1.1</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="D214" t="n">
-        <v>-33.78434889108475</v>
+        <v>-11.52350378740865</v>
       </c>
     </row>
     <row r="215">
@@ -3435,10 +3435,10 @@
         <v>1.1</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="D215" t="n">
-        <v>-17.19746097743489</v>
+        <v>-33.78434889108475</v>
       </c>
     </row>
     <row r="216">
@@ -3449,10 +3449,10 @@
         <v>1.1</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D216" t="n">
-        <v>-6.329827177057583</v>
+        <v>-17.19746097743489</v>
       </c>
     </row>
     <row r="217">
@@ -3463,10 +3463,10 @@
         <v>1.1</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D217" t="n">
-        <v>-14.54650273182927</v>
+        <v>-6.329827177057583</v>
       </c>
     </row>
     <row r="218">
@@ -3477,10 +3477,10 @@
         <v>1.1</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D218" t="n">
-        <v>16.30970776998776</v>
+        <v>-14.54650273182927</v>
       </c>
     </row>
     <row r="219">
@@ -3491,10 +3491,10 @@
         <v>1.1</v>
       </c>
       <c r="C219" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D219" t="n">
-        <v>24.00882805268154</v>
+        <v>16.30970776998776</v>
       </c>
     </row>
     <row r="220">
@@ -3505,10 +3505,10 @@
         <v>1.1</v>
       </c>
       <c r="C220" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>11.34361638072524</v>
+        <v>24.00882805268154</v>
       </c>
     </row>
     <row r="221">
@@ -3519,10 +3519,10 @@
         <v>1.1</v>
       </c>
       <c r="C221" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D221" t="n">
-        <v>20.34583240600429</v>
+        <v>11.34361638072524</v>
       </c>
     </row>
     <row r="222">
@@ -3533,10 +3533,10 @@
         <v>1.1</v>
       </c>
       <c r="C222" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D222" t="n">
-        <v>6.944038309892764</v>
+        <v>20.34583240600429</v>
       </c>
     </row>
     <row r="223">
@@ -3544,13 +3544,13 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D223" t="n">
-        <v>19.3669824082265</v>
+        <v>6.944038309892764</v>
       </c>
     </row>
     <row r="224">
@@ -3561,10 +3561,10 @@
         <v>1.2</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D224" t="n">
-        <v>16.03281290805518</v>
+        <v>19.3669824082265</v>
       </c>
     </row>
     <row r="225">
@@ -3575,10 +3575,10 @@
         <v>1.2</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="D225" t="n">
-        <v>3.232635306549387</v>
+        <v>16.03281290805518</v>
       </c>
     </row>
     <row r="226">
@@ -3589,10 +3589,10 @@
         <v>1.2</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D226" t="n">
-        <v>13.10476113223896</v>
+        <v>3.232635306549387</v>
       </c>
     </row>
     <row r="227">
@@ -3603,10 +3603,10 @@
         <v>1.2</v>
       </c>
       <c r="C227" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D227" t="n">
-        <v>17.06758547212501</v>
+        <v>13.10476113223896</v>
       </c>
     </row>
     <row r="228">
@@ -3617,10 +3617,10 @@
         <v>1.2</v>
       </c>
       <c r="C228" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0.222349113221143</v>
+        <v>17.06758547212501</v>
       </c>
     </row>
     <row r="229">
@@ -3631,10 +3631,10 @@
         <v>1.2</v>
       </c>
       <c r="C229" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D229" t="n">
-        <v>22.88014297715828</v>
+        <v>0.222349113221143</v>
       </c>
     </row>
     <row r="230">
@@ -3645,10 +3645,10 @@
         <v>1.2</v>
       </c>
       <c r="C230" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D230" t="n">
-        <v>10.9473752070705</v>
+        <v>22.88014297715828</v>
       </c>
     </row>
     <row r="231">
@@ -3659,10 +3659,10 @@
         <v>1.2</v>
       </c>
       <c r="C231" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D231" t="n">
-        <v>12.96867848991812</v>
+        <v>10.9473752070705</v>
       </c>
     </row>
     <row r="232">
@@ -3670,13 +3670,13 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D232" t="n">
-        <v>-16.93000735742697</v>
+        <v>12.96867848991812</v>
       </c>
     </row>
     <row r="233">
@@ -3687,10 +3687,10 @@
         <v>1.3</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="D233" t="n">
-        <v>-1.950876454962897</v>
+        <v>-16.93000735742697</v>
       </c>
     </row>
     <row r="234">
@@ -3701,10 +3701,10 @@
         <v>1.3</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D234" t="n">
-        <v>14.85167800881492</v>
+        <v>-1.950876454962897</v>
       </c>
     </row>
     <row r="235">
@@ -3715,10 +3715,10 @@
         <v>1.3</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D235" t="n">
-        <v>1.117566711180018</v>
+        <v>14.85167800881492</v>
       </c>
     </row>
     <row r="236">
@@ -3729,10 +3729,10 @@
         <v>1.3</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D236" t="n">
-        <v>0.1989775266321328</v>
+        <v>1.117566711180018</v>
       </c>
     </row>
     <row r="237">
@@ -3743,10 +3743,10 @@
         <v>1.3</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D237" t="n">
-        <v>11.99042792199484</v>
+        <v>0.1989775266321328</v>
       </c>
     </row>
     <row r="238">
@@ -3757,10 +3757,10 @@
         <v>1.3</v>
       </c>
       <c r="C238" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D238" t="n">
-        <v>17.8778675858085</v>
+        <v>11.99042792199484</v>
       </c>
     </row>
     <row r="239">
@@ -3771,10 +3771,10 @@
         <v>1.3</v>
       </c>
       <c r="C239" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>10.35218565937005</v>
+        <v>17.8778675858085</v>
       </c>
     </row>
     <row r="240">
@@ -3785,10 +3785,10 @@
         <v>1.3</v>
       </c>
       <c r="C240" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D240" t="n">
-        <v>14.2426594646236</v>
+        <v>10.35218565937005</v>
       </c>
     </row>
     <row r="241">
@@ -3796,13 +3796,13 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D241" t="n">
-        <v>-21.53664435089082</v>
+        <v>14.2426594646236</v>
       </c>
     </row>
     <row r="242">
@@ -3813,10 +3813,10 @@
         <v>1.4</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D242" t="n">
-        <v>9.328923873335238</v>
+        <v>-21.53664435089082</v>
       </c>
     </row>
     <row r="243">
@@ -3827,10 +3827,10 @@
         <v>1.4</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D243" t="n">
-        <v>10.10278720977517</v>
+        <v>9.328923873335238</v>
       </c>
     </row>
     <row r="244">
@@ -3841,10 +3841,10 @@
         <v>1.4</v>
       </c>
       <c r="C244" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D244" t="n">
-        <v>9.872864027314499</v>
+        <v>10.10278720977517</v>
       </c>
     </row>
     <row r="245">
@@ -3855,10 +3855,10 @@
         <v>1.4</v>
       </c>
       <c r="C245" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D245" t="n">
-        <v>32.99194919428567</v>
+        <v>9.872864027314499</v>
       </c>
     </row>
     <row r="246">
@@ -3869,10 +3869,10 @@
         <v>1.4</v>
       </c>
       <c r="C246" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D246" t="n">
-        <v>20.8988254865246</v>
+        <v>32.99194919428567</v>
       </c>
     </row>
     <row r="247">
@@ -3883,10 +3883,10 @@
         <v>1.4</v>
       </c>
       <c r="C247" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D247" t="n">
-        <v>21.02273262654837</v>
+        <v>20.8988254865246</v>
       </c>
     </row>
     <row r="248">
@@ -3894,13 +3894,13 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="C248" t="n">
-        <v>-1</v>
+        <v>0.3</v>
       </c>
       <c r="D248" t="n">
-        <v>-28.86385928028418</v>
+        <v>21.02273262654837</v>
       </c>
     </row>
     <row r="249">
@@ -3911,10 +3911,10 @@
         <v>1.5</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="D249" t="n">
-        <v>-27.92286274706721</v>
+        <v>-28.86385928028418</v>
       </c>
     </row>
     <row r="250">
@@ -3925,10 +3925,10 @@
         <v>1.5</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="D250" t="n">
-        <v>2.689054849903094</v>
+        <v>-27.92286274706721</v>
       </c>
     </row>
     <row r="251">
@@ -3939,10 +3939,10 @@
         <v>1.5</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D251" t="n">
-        <v>-3.238398508380039</v>
+        <v>2.689054849903094</v>
       </c>
     </row>
     <row r="252">
@@ -3953,10 +3953,10 @@
         <v>1.5</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D252" t="n">
-        <v>-10.63284974670976</v>
+        <v>-3.238398508380039</v>
       </c>
     </row>
     <row r="253">
@@ -3967,10 +3967,10 @@
         <v>1.5</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D253" t="n">
-        <v>12.06314032941557</v>
+        <v>-10.63284974670976</v>
       </c>
     </row>
     <row r="254">
@@ -3981,10 +3981,10 @@
         <v>1.5</v>
       </c>
       <c r="C254" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D254" t="n">
-        <v>15.39130549839703</v>
+        <v>12.06314032941557</v>
       </c>
     </row>
     <row r="255">
@@ -3992,13 +3992,13 @@
         <v>253</v>
       </c>
       <c r="B255" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="D255" t="n">
-        <v>30.06161708518444</v>
+        <v>15.39130549839703</v>
       </c>
     </row>
     <row r="256">
@@ -4009,10 +4009,10 @@
         <v>1.6</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D256" t="n">
-        <v>0.7047925256585673</v>
+        <v>30.06161708518444</v>
       </c>
     </row>
     <row r="257">
@@ -4023,10 +4023,10 @@
         <v>1.6</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D257" t="n">
-        <v>10.63291564194945</v>
+        <v>0.7047925256585673</v>
       </c>
     </row>
     <row r="258">
@@ -4037,10 +4037,10 @@
         <v>1.6</v>
       </c>
       <c r="C258" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D258" t="n">
-        <v>13.41141054228502</v>
+        <v>10.63291564194945</v>
       </c>
     </row>
     <row r="259">
@@ -4051,10 +4051,10 @@
         <v>1.6</v>
       </c>
       <c r="C259" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D259" t="n">
-        <v>1.650019604266784</v>
+        <v>13.41141054228502</v>
       </c>
     </row>
     <row r="260">
@@ -4065,10 +4065,10 @@
         <v>1.6</v>
       </c>
       <c r="C260" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D260" t="n">
-        <v>28.22846781771771</v>
+        <v>1.650019604266784</v>
       </c>
     </row>
     <row r="261">
@@ -4076,13 +4076,13 @@
         <v>259</v>
       </c>
       <c r="B261" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="C261" t="n">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
       <c r="D261" t="n">
-        <v>-18.77733988349265</v>
+        <v>28.22846781771771</v>
       </c>
     </row>
     <row r="262">
@@ -4093,10 +4093,10 @@
         <v>1.7</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="D262" t="n">
-        <v>21.84579337894117</v>
+        <v>-18.77733988349265</v>
       </c>
     </row>
     <row r="263">
@@ -4107,10 +4107,10 @@
         <v>1.7</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="D263" t="n">
-        <v>-19.66556972907224</v>
+        <v>21.84579337894117</v>
       </c>
     </row>
     <row r="264">
@@ -4121,10 +4121,10 @@
         <v>1.7</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="D264" t="n">
-        <v>-3.553466162428487</v>
+        <v>-19.66556972907224</v>
       </c>
     </row>
     <row r="265">
@@ -4135,10 +4135,10 @@
         <v>1.7</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="D265" t="n">
-        <v>13.31529204441477</v>
+        <v>-3.553466162428487</v>
       </c>
     </row>
     <row r="266">
@@ -4149,10 +4149,10 @@
         <v>1.7</v>
       </c>
       <c r="C266" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D266" t="n">
-        <v>7.676380537871452</v>
+        <v>13.31529204441477</v>
       </c>
     </row>
     <row r="267">
@@ -4163,10 +4163,10 @@
         <v>1.7</v>
       </c>
       <c r="C267" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D267" t="n">
-        <v>20.33047799727875</v>
+        <v>7.676380537871452</v>
       </c>
     </row>
     <row r="268">
@@ -4177,10 +4177,10 @@
         <v>1.7</v>
       </c>
       <c r="C268" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D268" t="n">
-        <v>-3.787252747789704</v>
+        <v>20.33047799727875</v>
       </c>
     </row>
     <row r="269">
@@ -4188,13 +4188,13 @@
         <v>267</v>
       </c>
       <c r="B269" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="C269" t="n">
-        <v>-1.1</v>
+        <v>0.2</v>
       </c>
       <c r="D269" t="n">
-        <v>-23.29234065333936</v>
+        <v>-3.787252747789704</v>
       </c>
     </row>
     <row r="270">
@@ -4205,10 +4205,10 @@
         <v>1.8</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="D270" t="n">
-        <v>-3.974652769615716</v>
+        <v>-23.29234065333936</v>
       </c>
     </row>
     <row r="271">
@@ -4219,10 +4219,10 @@
         <v>1.8</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D271" t="n">
-        <v>4.340558528281924</v>
+        <v>-3.974652769615716</v>
       </c>
     </row>
     <row r="272">
@@ -4233,10 +4233,10 @@
         <v>1.8</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D272" t="n">
-        <v>3.842592511862401</v>
+        <v>4.340558528281924</v>
       </c>
     </row>
     <row r="273">
@@ -4247,10 +4247,10 @@
         <v>1.8</v>
       </c>
       <c r="C273" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D273" t="n">
-        <v>15.54694213528108</v>
+        <v>3.842592511862401</v>
       </c>
     </row>
     <row r="274">
@@ -4261,10 +4261,10 @@
         <v>1.8</v>
       </c>
       <c r="C274" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D274" t="n">
-        <v>2.175129839142603</v>
+        <v>15.54694213528108</v>
       </c>
     </row>
     <row r="275">
@@ -4275,10 +4275,10 @@
         <v>1.8</v>
       </c>
       <c r="C275" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D275" t="n">
-        <v>-1.034435819286472</v>
+        <v>2.175129839142603</v>
       </c>
     </row>
     <row r="276">
@@ -4286,13 +4286,13 @@
         <v>274</v>
       </c>
       <c r="B276" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D276" t="n">
-        <v>-2.856228094308014</v>
+        <v>-1.034435819286472</v>
       </c>
     </row>
     <row r="277">
@@ -4303,10 +4303,10 @@
         <v>1.9</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D277" t="n">
-        <v>15.37696556690238</v>
+        <v>-2.856228094308014</v>
       </c>
     </row>
     <row r="278">
@@ -4317,10 +4317,10 @@
         <v>1.9</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D278" t="n">
-        <v>-13.45928790826484</v>
+        <v>15.37696556690238</v>
       </c>
     </row>
     <row r="279">
@@ -4331,10 +4331,10 @@
         <v>1.9</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D279" t="n">
-        <v>12.72257206711829</v>
+        <v>-13.45928790826484</v>
       </c>
     </row>
     <row r="280">
@@ -4342,13 +4342,13 @@
         <v>278</v>
       </c>
       <c r="B280" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="D280" t="n">
-        <v>13.78724913351632</v>
+        <v>12.72257206711829</v>
       </c>
     </row>
     <row r="281">
@@ -4359,10 +4359,10 @@
         <v>2</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="D281" t="n">
-        <v>18.72574927547594</v>
+        <v>13.78724913351632</v>
       </c>
     </row>
     <row r="282">
@@ -4373,10 +4373,10 @@
         <v>2</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D282" t="n">
-        <v>21.11336312725731</v>
+        <v>18.72574927547594</v>
       </c>
     </row>
     <row r="283">
@@ -4387,10 +4387,10 @@
         <v>2</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D283" t="n">
-        <v>17.39246112275586</v>
+        <v>21.11336312725731</v>
       </c>
     </row>
     <row r="284">
@@ -4401,10 +4401,10 @@
         <v>2</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D284" t="n">
-        <v>17.00766010495393</v>
+        <v>17.39246112275586</v>
       </c>
     </row>
     <row r="285">
@@ -4415,10 +4415,10 @@
         <v>2</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D285" t="n">
-        <v>-9.280344533884243</v>
+        <v>17.00766010495393</v>
       </c>
     </row>
     <row r="286">
@@ -4429,10 +4429,10 @@
         <v>2</v>
       </c>
       <c r="C286" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="D286" t="n">
-        <v>16.43776248864852</v>
+        <v>-9.280344533884243</v>
       </c>
     </row>
     <row r="287">
@@ -4440,13 +4440,13 @@
         <v>285</v>
       </c>
       <c r="B287" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D287" t="n">
-        <v>8.212539103417916</v>
+        <v>16.43776248864852</v>
       </c>
     </row>
     <row r="288">
@@ -4457,10 +4457,10 @@
         <v>2.1</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="D288" t="n">
-        <v>23.56968332972611</v>
+        <v>8.212539103417916</v>
       </c>
     </row>
     <row r="289">
@@ -4471,10 +4471,10 @@
         <v>2.1</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D289" t="n">
-        <v>17.61012028400106</v>
+        <v>23.56968332972611</v>
       </c>
     </row>
     <row r="290">
@@ -4485,10 +4485,10 @@
         <v>2.1</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D290" t="n">
-        <v>-13.79042182501424</v>
+        <v>17.61012028400106</v>
       </c>
     </row>
     <row r="291">
@@ -4499,10 +4499,10 @@
         <v>2.1</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D291" t="n">
-        <v>-6.992659577669663</v>
+        <v>-13.79042182501424</v>
       </c>
     </row>
     <row r="292">
@@ -4513,10 +4513,10 @@
         <v>2.1</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D292" t="n">
-        <v>26.48235627698286</v>
+        <v>-6.992659577669663</v>
       </c>
     </row>
     <row r="293">
@@ -4527,10 +4527,10 @@
         <v>2.1</v>
       </c>
       <c r="C293" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D293" t="n">
-        <v>-14.1103932017413</v>
+        <v>26.48235627698286</v>
       </c>
     </row>
     <row r="294">
@@ -4541,10 +4541,10 @@
         <v>2.1</v>
       </c>
       <c r="C294" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D294" t="n">
-        <v>9.425450655310886</v>
+        <v>-14.1103932017413</v>
       </c>
     </row>
     <row r="295">
@@ -4552,13 +4552,13 @@
         <v>293</v>
       </c>
       <c r="B295" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="D295" t="n">
-        <v>26.9891539335585</v>
+        <v>9.425450655310886</v>
       </c>
     </row>
     <row r="296">
@@ -4569,10 +4569,10 @@
         <v>2.2</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="D296" t="n">
-        <v>15.2980820925372</v>
+        <v>26.9891539335585</v>
       </c>
     </row>
     <row r="297">
@@ -4583,10 +4583,10 @@
         <v>2.2</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D297" t="n">
-        <v>9.381257126875875</v>
+        <v>15.2980820925372</v>
       </c>
     </row>
     <row r="298">
@@ -4597,10 +4597,10 @@
         <v>2.2</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D298" t="n">
-        <v>-4.878460416933283</v>
+        <v>9.381257126875875</v>
       </c>
     </row>
     <row r="299">
@@ -4611,10 +4611,10 @@
         <v>2.2</v>
       </c>
       <c r="C299" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="D299" t="n">
-        <v>-4.202882644640982</v>
+        <v>-4.878460416933283</v>
       </c>
     </row>
     <row r="300">
@@ -4622,13 +4622,13 @@
         <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="D300" t="n">
-        <v>30.23578444332056</v>
+        <v>-4.202882644640982</v>
       </c>
     </row>
     <row r="301">
@@ -4639,10 +4639,10 @@
         <v>2.3</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D301" t="n">
-        <v>-20.19643865448743</v>
+        <v>30.23578444332056</v>
       </c>
     </row>
     <row r="302">
@@ -4653,10 +4653,10 @@
         <v>2.3</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D302" t="n">
-        <v>-34.16261962418616</v>
+        <v>-20.19643865448743</v>
       </c>
     </row>
     <row r="303">
@@ -4664,13 +4664,13 @@
         <v>301</v>
       </c>
       <c r="B303" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="C303" t="n">
         <v>-0.1</v>
       </c>
       <c r="D303" t="n">
-        <v>-32.9675118294535</v>
+        <v>-34.16261962418616</v>
       </c>
     </row>
     <row r="304">
@@ -4681,10 +4681,10 @@
         <v>2.4</v>
       </c>
       <c r="C304" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D304" t="n">
-        <v>-9.091828309751271</v>
+        <v>-32.9675118294535</v>
       </c>
     </row>
     <row r="305">
@@ -4692,12 +4692,26 @@
         <v>303</v>
       </c>
       <c r="B305" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="C305" t="n">
         <v>0</v>
       </c>
       <c r="D305" t="n">
+        <v>-9.091828309751271</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
         <v>-4.236294380286648</v>
       </c>
     </row>
@@ -4982,13 +4996,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33D2ACFD-4858-4A0E-BB90-6074B6E8B8A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{636A9B1B-8861-4106-A81A-67C6DB0A6DFC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3832CD4F-AB17-49F6-9926-34BD9958807E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9626C816-84E5-48E1-95E9-53A58D076AA5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3891EA5D-F741-4189-A1BB-9B9B3CBDDD7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1F49372-1C9F-4622-8A1F-75E77F5710D0}"/>
 </file>